--- a/Hoàng/SALE/ĐƠN VỊ THỰC HIỆN/CÔNG TY CỔ PHẦN PHỤC VỤ MẶT ĐẤT SÀI GÒN - CHI NHÁNH ĐÀ NẴNG/2025/PHÂN TÍCH BG KSK - CÔNG TY CỔ PHẦN PHỤC VỤ MẶT ĐẤT SÀI GÒN 2025 (2).xlsx
+++ b/Hoàng/SALE/ĐƠN VỊ THỰC HIỆN/CÔNG TY CỔ PHẦN PHỤC VỤ MẶT ĐẤT SÀI GÒN - CHI NHÁNH ĐÀ NẴNG/2025/PHÂN TÍCH BG KSK - CÔNG TY CỔ PHẦN PHỤC VỤ MẶT ĐẤT SÀI GÒN 2025 (2).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\THIỆN NHÂN  HOSPITAL ( MINH DIỆP)\KHÁM SK ĐƠN VỊ\KSK ĐƠN VỊ 2025\BÁO GIÁ 2025\3. THÁNG 03.2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\SALE\ĐƠN VỊ THỰC HIỆN\CÔNG TY CỔ PHẦN PHỤC VỤ MẶT ĐẤT SÀI GÒN - CHI NHÁNH ĐÀ NẴNG\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A7E85D-ADD5-457C-8760-E67C873AC44D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1416E5D-06B5-4F2F-B02A-C4D860A15B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DV NGOÀI GÓI" sheetId="3" state="hidden" r:id="rId1"/>
@@ -27,10 +27,19 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'KHÁM NGHỀ NGHIỆP'!#REF!</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'KSK ĐỊNH KỲ'!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcOnSave="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -2353,195 +2362,251 @@
     <xf numFmtId="3" fontId="12" fillId="6" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="9" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="15" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="15" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="15" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="12" fillId="6" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="12" fillId="6" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="12" fillId="6" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2551,57 +2616,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="6" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="6" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="6" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2611,11 +2625,6 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma 2" xfId="1" xr:uid="{34A4EEE6-5F54-4F53-9D5B-42613882802D}"/>
@@ -3147,62 +3156,62 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K203"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="19" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" style="122" customWidth="1"/>
-    <col min="3" max="3" width="53.33203125" style="19" customWidth="1"/>
-    <col min="4" max="4" width="48.5546875" style="19" customWidth="1"/>
-    <col min="5" max="5" width="16.44140625" style="123" customWidth="1"/>
-    <col min="6" max="6" width="28.33203125" style="124" customWidth="1"/>
-    <col min="7" max="7" width="19.6640625" style="19" customWidth="1"/>
-    <col min="8" max="8" width="9.88671875" style="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.109375" style="19"/>
+    <col min="2" max="2" width="13.42578125" style="122" customWidth="1"/>
+    <col min="3" max="3" width="53.28515625" style="19" customWidth="1"/>
+    <col min="4" max="4" width="48.5703125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" style="123" customWidth="1"/>
+    <col min="6" max="6" width="28.28515625" style="124" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" style="19" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="181" t="s">
+      <c r="D1" s="150" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="182"/>
-      <c r="F1" s="183"/>
-    </row>
-    <row r="2" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E1" s="151"/>
+      <c r="F1" s="152"/>
+    </row>
+    <row r="2" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="181"/>
-      <c r="E2" s="182"/>
-      <c r="F2" s="183"/>
-    </row>
-    <row r="3" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D2" s="150"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="152"/>
+    </row>
+    <row r="3" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="181"/>
-      <c r="E3" s="182"/>
-      <c r="F3" s="183"/>
-    </row>
-    <row r="4" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D3" s="150"/>
+      <c r="E3" s="151"/>
+      <c r="F3" s="152"/>
+    </row>
+    <row r="4" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="181"/>
-      <c r="E4" s="182"/>
-      <c r="F4" s="183"/>
-    </row>
-    <row r="5" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D4" s="150"/>
+      <c r="E4" s="151"/>
+      <c r="F4" s="152"/>
+    </row>
+    <row r="5" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="184"/>
-      <c r="E5" s="185"/>
-      <c r="F5" s="186"/>
-    </row>
-    <row r="6" spans="1:11" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="D5" s="153"/>
+      <c r="E5" s="154"/>
+      <c r="F5" s="155"/>
+    </row>
+    <row r="6" spans="1:11" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -3210,22 +3219,22 @@
       <c r="E6" s="7"/>
       <c r="F6" s="5"/>
     </row>
-    <row r="7" spans="1:11" s="4" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A7" s="187" t="s">
+    <row r="7" spans="1:11" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="156" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="188"/>
-      <c r="C7" s="188"/>
-      <c r="D7" s="188"/>
-      <c r="E7" s="188"/>
-      <c r="F7" s="189"/>
+      <c r="B7" s="157"/>
+      <c r="C7" s="157"/>
+      <c r="D7" s="157"/>
+      <c r="E7" s="157"/>
+      <c r="F7" s="158"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
     </row>
-    <row r="8" spans="1:11" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -3238,49 +3247,49 @@
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
     </row>
-    <row r="9" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
-      <c r="B9" s="190" t="s">
+      <c r="B9" s="159" t="s">
         <v>409</v>
       </c>
-      <c r="C9" s="191"/>
-      <c r="D9" s="191"/>
-      <c r="E9" s="191"/>
-      <c r="F9" s="192"/>
+      <c r="C9" s="160"/>
+      <c r="D9" s="160"/>
+      <c r="E9" s="160"/>
+      <c r="F9" s="161"/>
       <c r="G9" s="12"/>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
     </row>
-    <row r="10" spans="1:11" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="193" t="s">
+    <row r="10" spans="1:11" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="162" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="194"/>
-      <c r="C10" s="194"/>
-      <c r="D10" s="194"/>
-      <c r="E10" s="194"/>
-      <c r="F10" s="195"/>
+      <c r="B10" s="163"/>
+      <c r="C10" s="163"/>
+      <c r="D10" s="163"/>
+      <c r="E10" s="163"/>
+      <c r="F10" s="164"/>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
     </row>
-    <row r="11" spans="1:11" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="196"/>
-      <c r="B11" s="197"/>
-      <c r="C11" s="197"/>
-      <c r="D11" s="197"/>
-      <c r="E11" s="197"/>
-      <c r="F11" s="198"/>
+    <row r="11" spans="1:11" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="165"/>
+      <c r="B11" s="166"/>
+      <c r="C11" s="166"/>
+      <c r="D11" s="166"/>
+      <c r="E11" s="166"/>
+      <c r="F11" s="167"/>
       <c r="G11" s="14"/>
       <c r="H11" s="14"/>
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
       <c r="K11" s="14"/>
     </row>
-    <row r="12" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="15"/>
@@ -3288,7 +3297,7 @@
       <c r="E12" s="17"/>
       <c r="F12" s="18"/>
     </row>
-    <row r="13" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A13" s="42"/>
       <c r="B13" s="43"/>
       <c r="C13" s="44"/>
@@ -3297,7 +3306,7 @@
       <c r="F13" s="46"/>
       <c r="G13" s="27"/>
     </row>
-    <row r="14" spans="1:11" s="52" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" s="52" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A14" s="47" t="s">
         <v>39</v>
       </c>
@@ -3308,7 +3317,7 @@
       <c r="F14" s="50"/>
       <c r="G14" s="51"/>
     </row>
-    <row r="15" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A15" s="53"/>
       <c r="B15" s="54"/>
       <c r="C15" s="55"/>
@@ -3317,14 +3326,14 @@
       <c r="F15" s="57"/>
       <c r="G15" s="27"/>
     </row>
-    <row r="16" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="199" t="s">
+      <c r="B16" s="168" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="200"/>
+      <c r="C16" s="169"/>
       <c r="D16" s="58" t="s">
         <v>5</v>
       </c>
@@ -3336,7 +3345,7 @@
       </c>
       <c r="G16" s="27"/>
     </row>
-    <row r="17" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="60" t="s">
         <v>40</v>
       </c>
@@ -3347,7 +3356,7 @@
       <c r="F17" s="65"/>
       <c r="G17" s="27"/>
     </row>
-    <row r="18" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A18" s="29">
         <f>IF(LEN(C18)=0,"",COUNTA($C$18:C18))</f>
         <v>1</v>
@@ -3367,7 +3376,7 @@
       <c r="F18" s="34"/>
       <c r="G18" s="27"/>
     </row>
-    <row r="19" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A19" s="29">
         <f>IF(LEN(C19)=0,"",COUNTA($C$18:C19))</f>
         <v>2</v>
@@ -3387,7 +3396,7 @@
       <c r="F19" s="34"/>
       <c r="G19" s="27"/>
     </row>
-    <row r="20" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A20" s="29">
         <f>IF(LEN(C20)=0,"",COUNTA($C$18:C20))</f>
         <v>3</v>
@@ -3407,7 +3416,7 @@
       <c r="F20" s="34"/>
       <c r="G20" s="27"/>
     </row>
-    <row r="21" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A21" s="29">
         <f>IF(LEN(C21)=0,"",COUNTA($C$18:C21))</f>
         <v>4</v>
@@ -3429,7 +3438,7 @@
       </c>
       <c r="G21" s="27"/>
     </row>
-    <row r="22" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A22" s="29">
         <f>IF(LEN(C22)=0,"",COUNTA($C$18:C22))</f>
         <v>5</v>
@@ -3447,7 +3456,7 @@
       <c r="F22" s="70"/>
       <c r="G22" s="27"/>
     </row>
-    <row r="23" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A23" s="29">
         <f>IF(LEN(C23)=0,"",COUNTA($C$18:C23))</f>
         <v>6</v>
@@ -3467,12 +3476,12 @@
       <c r="F23" s="34"/>
       <c r="G23" s="27"/>
     </row>
-    <row r="24" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="29">
         <f>IF(LEN(C24)=0,"",COUNTA($C$18:C24))</f>
         <v>7</v>
       </c>
-      <c r="B24" s="160" t="s">
+      <c r="B24" s="170" t="s">
         <v>65</v>
       </c>
       <c r="C24" s="24" t="s">
@@ -3484,17 +3493,17 @@
       <c r="E24" s="71">
         <v>62000</v>
       </c>
-      <c r="F24" s="152" t="s">
+      <c r="F24" s="173" t="s">
         <v>68</v>
       </c>
       <c r="G24" s="27"/>
     </row>
-    <row r="25" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A25" s="29">
         <f>IF(LEN(C25)=0,"",COUNTA($C$18:C25))</f>
         <v>8</v>
       </c>
-      <c r="B25" s="161"/>
+      <c r="B25" s="171"/>
       <c r="C25" s="24" t="s">
         <v>69</v>
       </c>
@@ -3504,15 +3513,15 @@
       <c r="E25" s="71">
         <v>165000</v>
       </c>
-      <c r="F25" s="153"/>
+      <c r="F25" s="174"/>
       <c r="G25" s="27"/>
     </row>
-    <row r="26" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A26" s="29">
         <f>IF(LEN(C26)=0,"",COUNTA($C$18:C26))</f>
         <v>9</v>
       </c>
-      <c r="B26" s="162"/>
+      <c r="B26" s="172"/>
       <c r="C26" s="24" t="s">
         <v>71</v>
       </c>
@@ -3522,15 +3531,15 @@
       <c r="E26" s="71">
         <v>116000</v>
       </c>
-      <c r="F26" s="154"/>
+      <c r="F26" s="175"/>
       <c r="G26" s="27"/>
     </row>
-    <row r="27" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A27" s="29">
         <f>IF(LEN(C27)=0,"",COUNTA($C$18:C27))</f>
         <v>10</v>
       </c>
-      <c r="B27" s="160" t="s">
+      <c r="B27" s="170" t="s">
         <v>73</v>
       </c>
       <c r="C27" s="24" t="s">
@@ -3545,12 +3554,12 @@
       <c r="F27" s="34"/>
       <c r="G27" s="27"/>
     </row>
-    <row r="28" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A28" s="29">
         <f>IF(LEN(C28)=0,"",COUNTA($C$18:C28))</f>
         <v>11</v>
       </c>
-      <c r="B28" s="161"/>
+      <c r="B28" s="171"/>
       <c r="C28" s="24" t="s">
         <v>76</v>
       </c>
@@ -3560,17 +3569,17 @@
       <c r="E28" s="71">
         <v>130000</v>
       </c>
-      <c r="F28" s="152" t="s">
+      <c r="F28" s="173" t="s">
         <v>68</v>
       </c>
       <c r="G28" s="27"/>
     </row>
-    <row r="29" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A29" s="29">
         <f>IF(LEN(C29)=0,"",COUNTA($C$18:C29))</f>
         <v>12</v>
       </c>
-      <c r="B29" s="161"/>
+      <c r="B29" s="171"/>
       <c r="C29" s="24" t="s">
         <v>77</v>
       </c>
@@ -3580,15 +3589,15 @@
       <c r="E29" s="71">
         <v>120000</v>
       </c>
-      <c r="F29" s="153"/>
+      <c r="F29" s="174"/>
       <c r="G29" s="27"/>
     </row>
-    <row r="30" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A30" s="29">
         <f>IF(LEN(C30)=0,"",COUNTA($C$18:C30))</f>
         <v>13</v>
       </c>
-      <c r="B30" s="162"/>
+      <c r="B30" s="172"/>
       <c r="C30" s="24" t="s">
         <v>78</v>
       </c>
@@ -3598,10 +3607,10 @@
       <c r="E30" s="71">
         <v>282000</v>
       </c>
-      <c r="F30" s="154"/>
+      <c r="F30" s="175"/>
       <c r="G30" s="27"/>
     </row>
-    <row r="31" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A31" s="29">
         <f>IF(LEN(C31)=0,"",COUNTA($C$18:C31))</f>
         <v>14</v>
@@ -3621,12 +3630,12 @@
       <c r="F31" s="34"/>
       <c r="G31" s="27"/>
     </row>
-    <row r="32" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="29">
         <f>IF(LEN(C32)=0,"",COUNTA($C$18:C32))</f>
         <v>15</v>
       </c>
-      <c r="B32" s="164" t="s">
+      <c r="B32" s="146" t="s">
         <v>83</v>
       </c>
       <c r="C32" s="24" t="s">
@@ -3638,17 +3647,17 @@
       <c r="E32" s="71">
         <v>71000</v>
       </c>
-      <c r="F32" s="179" t="s">
+      <c r="F32" s="148" t="s">
         <v>86</v>
       </c>
       <c r="G32" s="27"/>
     </row>
-    <row r="33" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A33" s="29">
         <f>IF(LEN(C33)=0,"",COUNTA($C$18:C33))</f>
         <v>16</v>
       </c>
-      <c r="B33" s="165"/>
+      <c r="B33" s="147"/>
       <c r="C33" s="24" t="s">
         <v>87</v>
       </c>
@@ -3658,10 +3667,10 @@
       <c r="E33" s="66">
         <v>138000</v>
       </c>
-      <c r="F33" s="180"/>
+      <c r="F33" s="149"/>
       <c r="G33" s="27"/>
     </row>
-    <row r="34" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A34" s="29">
         <f>IF(LEN(C34)=0,"",COUNTA($C$18:C34))</f>
         <v>17</v>
@@ -3681,12 +3690,12 @@
       <c r="F34" s="73"/>
       <c r="G34" s="27"/>
     </row>
-    <row r="35" spans="1:7" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="29">
         <f>IF(LEN(C35)=0,"",COUNTA($C$18:C35))</f>
         <v>18</v>
       </c>
-      <c r="B35" s="167" t="s">
+      <c r="B35" s="177" t="s">
         <v>92</v>
       </c>
       <c r="C35" s="24" t="s">
@@ -3698,17 +3707,17 @@
       <c r="E35" s="71">
         <v>30000</v>
       </c>
-      <c r="F35" s="168" t="s">
+      <c r="F35" s="178" t="s">
         <v>95</v>
       </c>
       <c r="G35" s="51"/>
     </row>
-    <row r="36" spans="1:7" s="52" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" s="52" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A36" s="29">
         <f>IF(LEN(C36)=0,"",COUNTA($C$18:C36))</f>
         <v>19</v>
       </c>
-      <c r="B36" s="167"/>
+      <c r="B36" s="177"/>
       <c r="C36" s="24" t="s">
         <v>96</v>
       </c>
@@ -3718,10 +3727,10 @@
       <c r="E36" s="71">
         <v>20000</v>
       </c>
-      <c r="F36" s="169"/>
+      <c r="F36" s="179"/>
       <c r="G36" s="51"/>
     </row>
-    <row r="37" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A37" s="74" t="s">
         <v>97</v>
       </c>
@@ -3732,12 +3741,12 @@
       <c r="F37" s="65"/>
       <c r="G37" s="27"/>
     </row>
-    <row r="38" spans="1:7" s="52" customFormat="1" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" s="52" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A38" s="29">
         <f>IF(LEN(C38)=0,"",COUNTA($C$18:C38))</f>
         <v>20</v>
       </c>
-      <c r="B38" s="170" t="s">
+      <c r="B38" s="180" t="s">
         <v>98</v>
       </c>
       <c r="C38" s="77" t="s">
@@ -3752,12 +3761,12 @@
       <c r="F38" s="34"/>
       <c r="G38" s="51"/>
     </row>
-    <row r="39" spans="1:7" s="52" customFormat="1" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" s="52" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A39" s="29">
         <f>IF(LEN(C39)=0,"",COUNTA($C$18:C39))</f>
         <v>21</v>
       </c>
-      <c r="B39" s="171"/>
+      <c r="B39" s="181"/>
       <c r="C39" s="77" t="s">
         <v>101</v>
       </c>
@@ -3770,12 +3779,12 @@
       <c r="F39" s="34"/>
       <c r="G39" s="51"/>
     </row>
-    <row r="40" spans="1:7" s="52" customFormat="1" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" s="52" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A40" s="29">
         <f>IF(LEN(C40)=0,"",COUNTA($C$18:C40))</f>
         <v>22</v>
       </c>
-      <c r="B40" s="171"/>
+      <c r="B40" s="181"/>
       <c r="C40" s="77" t="s">
         <v>103</v>
       </c>
@@ -3788,12 +3797,12 @@
       <c r="F40" s="34"/>
       <c r="G40" s="51"/>
     </row>
-    <row r="41" spans="1:7" s="52" customFormat="1" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" s="52" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A41" s="29">
         <f>IF(LEN(C41)=0,"",COUNTA($C$18:C41))</f>
         <v>23</v>
       </c>
-      <c r="B41" s="171"/>
+      <c r="B41" s="181"/>
       <c r="C41" s="77" t="s">
         <v>105</v>
       </c>
@@ -3806,12 +3815,12 @@
       <c r="F41" s="34"/>
       <c r="G41" s="51"/>
     </row>
-    <row r="42" spans="1:7" s="52" customFormat="1" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" s="52" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A42" s="29">
         <f>IF(LEN(C42)=0,"",COUNTA($C$18:C42))</f>
         <v>24</v>
       </c>
-      <c r="B42" s="171"/>
+      <c r="B42" s="181"/>
       <c r="C42" s="77" t="s">
         <v>107</v>
       </c>
@@ -3824,12 +3833,12 @@
       <c r="F42" s="34"/>
       <c r="G42" s="51"/>
     </row>
-    <row r="43" spans="1:7" s="52" customFormat="1" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" s="52" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A43" s="29">
         <f>IF(LEN(C43)=0,"",COUNTA($C$18:C43))</f>
         <v>25</v>
       </c>
-      <c r="B43" s="171"/>
+      <c r="B43" s="181"/>
       <c r="C43" s="77" t="s">
         <v>109</v>
       </c>
@@ -3842,12 +3851,12 @@
       <c r="F43" s="34"/>
       <c r="G43" s="51"/>
     </row>
-    <row r="44" spans="1:7" s="52" customFormat="1" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" s="52" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A44" s="29">
         <f>IF(LEN(C44)=0,"",COUNTA($C$18:C44))</f>
         <v>26</v>
       </c>
-      <c r="B44" s="171"/>
+      <c r="B44" s="181"/>
       <c r="C44" s="77" t="s">
         <v>111</v>
       </c>
@@ -3862,12 +3871,12 @@
       </c>
       <c r="G44" s="51"/>
     </row>
-    <row r="45" spans="1:7" s="52" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" s="52" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A45" s="29">
         <f>IF(LEN(C45)=0,"",COUNTA($C$18:C45))</f>
         <v>27</v>
       </c>
-      <c r="B45" s="171"/>
+      <c r="B45" s="181"/>
       <c r="C45" s="81" t="s">
         <v>114</v>
       </c>
@@ -3880,12 +3889,12 @@
       <c r="F45" s="34"/>
       <c r="G45" s="51"/>
     </row>
-    <row r="46" spans="1:7" s="52" customFormat="1" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" s="52" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A46" s="29">
         <f>IF(LEN(C46)=0,"",COUNTA($C$18:C46))</f>
         <v>28</v>
       </c>
-      <c r="B46" s="171"/>
+      <c r="B46" s="181"/>
       <c r="C46" s="77" t="s">
         <v>116</v>
       </c>
@@ -3900,12 +3909,12 @@
       </c>
       <c r="G46" s="27"/>
     </row>
-    <row r="47" spans="1:7" s="52" customFormat="1" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" s="52" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A47" s="29">
         <f>IF(LEN(C47)=0,"",COUNTA($C$18:C47))</f>
         <v>29</v>
       </c>
-      <c r="B47" s="171"/>
+      <c r="B47" s="181"/>
       <c r="C47" s="77" t="s">
         <v>119</v>
       </c>
@@ -3918,12 +3927,12 @@
       <c r="F47" s="34"/>
       <c r="G47" s="51"/>
     </row>
-    <row r="48" spans="1:7" s="52" customFormat="1" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" s="52" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A48" s="29">
         <f>IF(LEN(C48)=0,"",COUNTA($C$18:C48))</f>
         <v>30</v>
       </c>
-      <c r="B48" s="171"/>
+      <c r="B48" s="181"/>
       <c r="C48" s="77" t="s">
         <v>121</v>
       </c>
@@ -3936,12 +3945,12 @@
       <c r="F48" s="34"/>
       <c r="G48" s="51"/>
     </row>
-    <row r="49" spans="1:7" s="52" customFormat="1" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" s="52" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A49" s="29">
         <f>IF(LEN(C49)=0,"",COUNTA($C$18:C49))</f>
         <v>31</v>
       </c>
-      <c r="B49" s="171"/>
+      <c r="B49" s="181"/>
       <c r="C49" s="77" t="s">
         <v>123</v>
       </c>
@@ -3954,12 +3963,12 @@
       <c r="F49" s="34"/>
       <c r="G49" s="51"/>
     </row>
-    <row r="50" spans="1:7" s="52" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" s="52" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A50" s="29">
         <f>IF(LEN(C50)=0,"",COUNTA($C$18:C50))</f>
         <v>32</v>
       </c>
-      <c r="B50" s="172"/>
+      <c r="B50" s="182"/>
       <c r="C50" s="77" t="s">
         <v>125</v>
       </c>
@@ -3972,72 +3981,72 @@
       <c r="F50" s="34"/>
       <c r="G50" s="51"/>
     </row>
-    <row r="51" spans="1:7" s="52" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" s="52" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="29">
         <f>IF(LEN(C51)=0,"",COUNTA($C$18:C51))</f>
         <v>33</v>
       </c>
-      <c r="B51" s="170" t="s">
+      <c r="B51" s="180" t="s">
         <v>127</v>
       </c>
       <c r="C51" s="77" t="s">
         <v>128</v>
       </c>
-      <c r="D51" s="173" t="s">
+      <c r="D51" s="183" t="s">
         <v>129</v>
       </c>
       <c r="E51" s="33">
         <v>137000</v>
       </c>
-      <c r="F51" s="152" t="s">
+      <c r="F51" s="173" t="s">
         <v>130</v>
       </c>
       <c r="G51" s="51"/>
     </row>
-    <row r="52" spans="1:7" s="52" customFormat="1" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" s="52" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A52" s="29">
         <f>IF(LEN(C52)=0,"",COUNTA($C$18:C52))</f>
         <v>34</v>
       </c>
-      <c r="B52" s="171"/>
+      <c r="B52" s="181"/>
       <c r="C52" s="77" t="s">
         <v>131</v>
       </c>
-      <c r="D52" s="174"/>
+      <c r="D52" s="184"/>
       <c r="E52" s="33">
         <v>137000</v>
       </c>
-      <c r="F52" s="153"/>
+      <c r="F52" s="174"/>
       <c r="G52" s="51"/>
     </row>
-    <row r="53" spans="1:7" s="52" customFormat="1" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" s="52" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A53" s="29">
         <f>IF(LEN(C53)=0,"",COUNTA($C$18:C53))</f>
         <v>35</v>
       </c>
-      <c r="B53" s="172"/>
+      <c r="B53" s="182"/>
       <c r="C53" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="D53" s="175"/>
+      <c r="D53" s="185"/>
       <c r="E53" s="33">
         <v>208000</v>
       </c>
-      <c r="F53" s="154"/>
+      <c r="F53" s="175"/>
       <c r="G53" s="51"/>
     </row>
-    <row r="54" spans="1:7" s="52" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" s="52" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A54" s="29">
         <f>IF(LEN(C54)=0,"",COUNTA($C$18:C54))</f>
         <v>36</v>
       </c>
-      <c r="B54" s="170" t="s">
+      <c r="B54" s="180" t="s">
         <v>133</v>
       </c>
       <c r="C54" s="77" t="s">
         <v>134</v>
       </c>
-      <c r="D54" s="176" t="s">
+      <c r="D54" s="186" t="s">
         <v>135</v>
       </c>
       <c r="E54" s="33">
@@ -4046,28 +4055,28 @@
       <c r="F54" s="84"/>
       <c r="G54" s="51"/>
     </row>
-    <row r="55" spans="1:7" s="52" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" s="52" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A55" s="29">
         <f>IF(LEN(C55)=0,"",COUNTA($C$18:C55))</f>
         <v>37</v>
       </c>
-      <c r="B55" s="171"/>
+      <c r="B55" s="181"/>
       <c r="C55" s="77" t="s">
         <v>136</v>
       </c>
-      <c r="D55" s="177"/>
+      <c r="D55" s="187"/>
       <c r="E55" s="33">
         <v>323000</v>
       </c>
       <c r="F55" s="84"/>
       <c r="G55" s="51"/>
     </row>
-    <row r="56" spans="1:7" s="52" customFormat="1" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" s="52" customFormat="1" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="29">
         <f>IF(LEN(C56)=0,"",COUNTA($C$18:C56))</f>
         <v>38</v>
       </c>
-      <c r="B56" s="171"/>
+      <c r="B56" s="181"/>
       <c r="C56" s="77" t="s">
         <v>137</v>
       </c>
@@ -4080,12 +4089,12 @@
       <c r="F56" s="84"/>
       <c r="G56" s="51"/>
     </row>
-    <row r="57" spans="1:7" s="52" customFormat="1" ht="84" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" s="52" customFormat="1" ht="66" x14ac:dyDescent="0.25">
       <c r="A57" s="29">
         <f>IF(LEN(C57)=0,"",COUNTA($C$18:C57))</f>
         <v>39</v>
       </c>
-      <c r="B57" s="172"/>
+      <c r="B57" s="182"/>
       <c r="C57" s="77" t="s">
         <v>139</v>
       </c>
@@ -4098,23 +4107,23 @@
       <c r="F57" s="84"/>
       <c r="G57" s="51"/>
     </row>
-    <row r="58" spans="1:7" s="52" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A58" s="147" t="s">
+    <row r="58" spans="1:7" s="52" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A58" s="188" t="s">
         <v>141</v>
       </c>
-      <c r="B58" s="148"/>
-      <c r="C58" s="148"/>
-      <c r="D58" s="149"/>
+      <c r="B58" s="189"/>
+      <c r="C58" s="189"/>
+      <c r="D58" s="190"/>
       <c r="E58" s="64"/>
       <c r="F58" s="65"/>
       <c r="G58" s="51"/>
     </row>
-    <row r="59" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A59" s="29">
         <f>IF(LEN(C59)=0,"",COUNTA($C$18:C59))</f>
         <v>40</v>
       </c>
-      <c r="B59" s="178"/>
+      <c r="B59" s="191"/>
       <c r="C59" s="24" t="s">
         <v>144</v>
       </c>
@@ -4127,12 +4136,12 @@
       <c r="F59" s="34"/>
       <c r="G59" s="27"/>
     </row>
-    <row r="60" spans="1:7" ht="117.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" ht="115.5" x14ac:dyDescent="0.25">
       <c r="A60" s="29">
         <f>IF(LEN(C60)=0,"",COUNTA($C$18:C60))</f>
         <v>41</v>
       </c>
-      <c r="B60" s="178"/>
+      <c r="B60" s="191"/>
       <c r="C60" s="24" t="s">
         <v>146</v>
       </c>
@@ -4147,12 +4156,12 @@
       </c>
       <c r="G60" s="27"/>
     </row>
-    <row r="61" spans="1:7" ht="117.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" ht="115.5" x14ac:dyDescent="0.25">
       <c r="A61" s="29">
         <f>IF(LEN(C61)=0,"",COUNTA($C$18:C61))</f>
         <v>42</v>
       </c>
-      <c r="B61" s="178"/>
+      <c r="B61" s="191"/>
       <c r="C61" s="24" t="s">
         <v>149</v>
       </c>
@@ -4167,12 +4176,12 @@
       </c>
       <c r="G61" s="27"/>
     </row>
-    <row r="62" spans="1:7" ht="151.19999999999999" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" ht="148.5" x14ac:dyDescent="0.25">
       <c r="A62" s="29">
         <f>IF(LEN(C62)=0,"",COUNTA($C$18:C62))</f>
         <v>43</v>
       </c>
-      <c r="B62" s="178"/>
+      <c r="B62" s="191"/>
       <c r="C62" s="24" t="s">
         <v>151</v>
       </c>
@@ -4185,12 +4194,12 @@
       <c r="F62" s="34"/>
       <c r="G62" s="27"/>
     </row>
-    <row r="63" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A63" s="29">
         <f>IF(LEN(C63)=0,"",COUNTA($C$18:C63))</f>
         <v>44</v>
       </c>
-      <c r="B63" s="178"/>
+      <c r="B63" s="191"/>
       <c r="C63" s="24" t="s">
         <v>153</v>
       </c>
@@ -4205,12 +4214,12 @@
       </c>
       <c r="G63" s="27"/>
     </row>
-    <row r="64" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A64" s="29">
         <f>IF(LEN(C64)=0,"",COUNTA($C$18:C64))</f>
         <v>45</v>
       </c>
-      <c r="B64" s="178"/>
+      <c r="B64" s="191"/>
       <c r="C64" s="24" t="s">
         <v>156</v>
       </c>
@@ -4225,12 +4234,12 @@
       </c>
       <c r="G64" s="27"/>
     </row>
-    <row r="65" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A65" s="29">
         <f>IF(LEN(C65)=0,"",COUNTA($C$18:C65))</f>
         <v>46</v>
       </c>
-      <c r="B65" s="178"/>
+      <c r="B65" s="191"/>
       <c r="C65" s="24" t="s">
         <v>159</v>
       </c>
@@ -4245,12 +4254,12 @@
       </c>
       <c r="G65" s="27"/>
     </row>
-    <row r="66" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A66" s="29">
         <f>IF(LEN(C66)=0,"",COUNTA($C$18:C66))</f>
         <v>47</v>
       </c>
-      <c r="B66" s="178" t="s">
+      <c r="B66" s="191" t="s">
         <v>162</v>
       </c>
       <c r="C66" s="24" t="s">
@@ -4265,12 +4274,12 @@
       <c r="F66" s="34"/>
       <c r="G66" s="27"/>
     </row>
-    <row r="67" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A67" s="29">
         <f>IF(LEN(C67)=0,"",COUNTA($C$18:C67))</f>
         <v>48</v>
       </c>
-      <c r="B67" s="178"/>
+      <c r="B67" s="191"/>
       <c r="C67" s="24" t="s">
         <v>165</v>
       </c>
@@ -4283,12 +4292,12 @@
       <c r="F67" s="34"/>
       <c r="G67" s="27"/>
     </row>
-    <row r="68" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A68" s="29">
         <f>IF(LEN(C68)=0,"",COUNTA($C$18:C68))</f>
         <v>49</v>
       </c>
-      <c r="B68" s="164" t="s">
+      <c r="B68" s="146" t="s">
         <v>167</v>
       </c>
       <c r="C68" s="24" t="s">
@@ -4303,12 +4312,12 @@
       <c r="F68" s="34"/>
       <c r="G68" s="27"/>
     </row>
-    <row r="69" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A69" s="29">
         <f>IF(LEN(C69)=0,"",COUNTA($C$18:C69))</f>
         <v>50</v>
       </c>
-      <c r="B69" s="166"/>
+      <c r="B69" s="176"/>
       <c r="C69" s="24" t="s">
         <v>170</v>
       </c>
@@ -4321,12 +4330,12 @@
       <c r="F69" s="34"/>
       <c r="G69" s="27"/>
     </row>
-    <row r="70" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A70" s="29">
         <f>IF(LEN(C70)=0,"",COUNTA($C$18:C70))</f>
         <v>51</v>
       </c>
-      <c r="B70" s="165"/>
+      <c r="B70" s="147"/>
       <c r="C70" s="24" t="s">
         <v>172</v>
       </c>
@@ -4339,23 +4348,23 @@
       <c r="F70" s="34"/>
       <c r="G70" s="27"/>
     </row>
-    <row r="71" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A71" s="147" t="s">
+    <row r="71" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A71" s="188" t="s">
         <v>174</v>
       </c>
-      <c r="B71" s="148"/>
-      <c r="C71" s="148"/>
-      <c r="D71" s="149"/>
+      <c r="B71" s="189"/>
+      <c r="C71" s="189"/>
+      <c r="D71" s="190"/>
       <c r="E71" s="87"/>
       <c r="F71" s="65"/>
       <c r="G71" s="27"/>
     </row>
-    <row r="72" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A72" s="29">
         <f>IF(LEN(C72)=0,"",COUNTA($C$18:C72))</f>
         <v>52</v>
       </c>
-      <c r="B72" s="160" t="s">
+      <c r="B72" s="170" t="s">
         <v>175</v>
       </c>
       <c r="C72" s="24" t="s">
@@ -4370,12 +4379,12 @@
       <c r="F72" s="34"/>
       <c r="G72" s="27"/>
     </row>
-    <row r="73" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A73" s="29">
         <f>IF(LEN(C73)=0,"",COUNTA($C$18:C73))</f>
         <v>53</v>
       </c>
-      <c r="B73" s="162"/>
+      <c r="B73" s="172"/>
       <c r="C73" s="24" t="s">
         <v>178</v>
       </c>
@@ -4388,12 +4397,12 @@
       <c r="F73" s="34"/>
       <c r="G73" s="27"/>
     </row>
-    <row r="74" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A74" s="29">
         <f>IF(LEN(C74)=0,"",COUNTA($C$18:C74))</f>
         <v>54</v>
       </c>
-      <c r="B74" s="164" t="s">
+      <c r="B74" s="146" t="s">
         <v>180</v>
       </c>
       <c r="C74" s="24" t="s">
@@ -4406,12 +4415,12 @@
       <c r="F74" s="34"/>
       <c r="G74" s="27"/>
     </row>
-    <row r="75" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A75" s="29">
         <f>IF(LEN(C75)=0,"",COUNTA($C$18:C75))</f>
         <v>55</v>
       </c>
-      <c r="B75" s="165"/>
+      <c r="B75" s="147"/>
       <c r="C75" s="24" t="s">
         <v>182</v>
       </c>
@@ -4422,7 +4431,7 @@
       <c r="F75" s="34"/>
       <c r="G75" s="27"/>
     </row>
-    <row r="76" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A76" s="29">
         <f>IF(LEN(C76)=0,"",COUNTA($C$18:C76))</f>
         <v>56</v>
@@ -4442,12 +4451,12 @@
       </c>
       <c r="G76" s="27"/>
     </row>
-    <row r="77" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A77" s="29">
         <f>IF(LEN(C77)=0,"",COUNTA($C$18:C77))</f>
         <v>57</v>
       </c>
-      <c r="B77" s="164" t="s">
+      <c r="B77" s="146" t="s">
         <v>186</v>
       </c>
       <c r="C77" s="24" t="s">
@@ -4460,12 +4469,12 @@
       <c r="F77" s="34"/>
       <c r="G77" s="27"/>
     </row>
-    <row r="78" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A78" s="29">
         <f>IF(LEN(C78)=0,"",COUNTA($C$18:C78))</f>
         <v>58</v>
       </c>
-      <c r="B78" s="166"/>
+      <c r="B78" s="176"/>
       <c r="C78" s="24" t="s">
         <v>188</v>
       </c>
@@ -4476,12 +4485,12 @@
       <c r="F78" s="34"/>
       <c r="G78" s="27"/>
     </row>
-    <row r="79" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A79" s="29">
         <f>IF(LEN(C79)=0,"",COUNTA($C$18:C79))</f>
         <v>59</v>
       </c>
-      <c r="B79" s="166"/>
+      <c r="B79" s="176"/>
       <c r="C79" s="24" t="s">
         <v>189</v>
       </c>
@@ -4492,12 +4501,12 @@
       <c r="F79" s="34"/>
       <c r="G79" s="27"/>
     </row>
-    <row r="80" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A80" s="29">
         <f>IF(LEN(C80)=0,"",COUNTA($C$18:C80))</f>
         <v>60</v>
       </c>
-      <c r="B80" s="166"/>
+      <c r="B80" s="176"/>
       <c r="C80" s="24" t="s">
         <v>190</v>
       </c>
@@ -4508,12 +4517,12 @@
       <c r="F80" s="34"/>
       <c r="G80" s="27"/>
     </row>
-    <row r="81" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A81" s="29">
         <f>IF(LEN(C81)=0,"",COUNTA($C$18:C81))</f>
         <v>61</v>
       </c>
-      <c r="B81" s="166"/>
+      <c r="B81" s="176"/>
       <c r="C81" s="24" t="s">
         <v>191</v>
       </c>
@@ -4524,12 +4533,12 @@
       <c r="F81" s="34"/>
       <c r="G81" s="27"/>
     </row>
-    <row r="82" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A82" s="29">
         <f>IF(LEN(C82)=0,"",COUNTA($C$18:C82))</f>
         <v>62</v>
       </c>
-      <c r="B82" s="166"/>
+      <c r="B82" s="176"/>
       <c r="C82" s="24" t="s">
         <v>192</v>
       </c>
@@ -4540,12 +4549,12 @@
       <c r="F82" s="34"/>
       <c r="G82" s="27"/>
     </row>
-    <row r="83" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A83" s="29">
         <f>IF(LEN(C83)=0,"",COUNTA($C$18:C83))</f>
         <v>63</v>
       </c>
-      <c r="B83" s="166"/>
+      <c r="B83" s="176"/>
       <c r="C83" s="24" t="s">
         <v>193</v>
       </c>
@@ -4556,12 +4565,12 @@
       <c r="F83" s="34"/>
       <c r="G83" s="27"/>
     </row>
-    <row r="84" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A84" s="29">
         <f>IF(LEN(C84)=0,"",COUNTA($C$18:C84))</f>
         <v>64</v>
       </c>
-      <c r="B84" s="166"/>
+      <c r="B84" s="176"/>
       <c r="C84" s="24" t="s">
         <v>194</v>
       </c>
@@ -4572,12 +4581,12 @@
       <c r="F84" s="34"/>
       <c r="G84" s="27"/>
     </row>
-    <row r="85" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A85" s="29">
         <f>IF(LEN(C85)=0,"",COUNTA($C$18:C85))</f>
         <v>65</v>
       </c>
-      <c r="B85" s="166"/>
+      <c r="B85" s="176"/>
       <c r="C85" s="24" t="s">
         <v>195</v>
       </c>
@@ -4588,12 +4597,12 @@
       <c r="F85" s="34"/>
       <c r="G85" s="27"/>
     </row>
-    <row r="86" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A86" s="29">
         <f>IF(LEN(C86)=0,"",COUNTA($C$18:C86))</f>
         <v>66</v>
       </c>
-      <c r="B86" s="166"/>
+      <c r="B86" s="176"/>
       <c r="C86" s="24" t="s">
         <v>196</v>
       </c>
@@ -4604,12 +4613,12 @@
       <c r="F86" s="34"/>
       <c r="G86" s="27"/>
     </row>
-    <row r="87" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A87" s="29">
         <f>IF(LEN(C87)=0,"",COUNTA($C$18:C87))</f>
         <v>67</v>
       </c>
-      <c r="B87" s="166"/>
+      <c r="B87" s="176"/>
       <c r="C87" s="24" t="s">
         <v>197</v>
       </c>
@@ -4620,12 +4629,12 @@
       <c r="F87" s="34"/>
       <c r="G87" s="27"/>
     </row>
-    <row r="88" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A88" s="29">
         <f>IF(LEN(C88)=0,"",COUNTA($C$18:C88))</f>
         <v>68</v>
       </c>
-      <c r="B88" s="166"/>
+      <c r="B88" s="176"/>
       <c r="C88" s="24" t="s">
         <v>198</v>
       </c>
@@ -4636,12 +4645,12 @@
       <c r="F88" s="34"/>
       <c r="G88" s="27"/>
     </row>
-    <row r="89" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A89" s="29">
         <f>IF(LEN(C89)=0,"",COUNTA($C$18:C89))</f>
         <v>69</v>
       </c>
-      <c r="B89" s="166"/>
+      <c r="B89" s="176"/>
       <c r="C89" s="24" t="s">
         <v>199</v>
       </c>
@@ -4652,12 +4661,12 @@
       <c r="F89" s="34"/>
       <c r="G89" s="27"/>
     </row>
-    <row r="90" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A90" s="29">
         <f>IF(LEN(C90)=0,"",COUNTA($C$18:C90))</f>
         <v>70</v>
       </c>
-      <c r="B90" s="165"/>
+      <c r="B90" s="147"/>
       <c r="C90" s="24" t="s">
         <v>200</v>
       </c>
@@ -4668,18 +4677,18 @@
       <c r="F90" s="34"/>
       <c r="G90" s="27"/>
     </row>
-    <row r="91" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A91" s="147" t="s">
+    <row r="91" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A91" s="188" t="s">
         <v>201</v>
       </c>
-      <c r="B91" s="148"/>
-      <c r="C91" s="148"/>
-      <c r="D91" s="149"/>
+      <c r="B91" s="189"/>
+      <c r="C91" s="189"/>
+      <c r="D91" s="190"/>
       <c r="E91" s="64"/>
       <c r="F91" s="65"/>
       <c r="G91" s="27"/>
     </row>
-    <row r="92" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A92" s="29">
         <f>IF(LEN(C92)=0,"",COUNTA($C$18:C92))</f>
         <v>71</v>
@@ -4699,7 +4708,7 @@
       <c r="F92" s="34"/>
       <c r="G92" s="27"/>
     </row>
-    <row r="93" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A93" s="29">
         <f>IF(LEN(C93)=0,"",COUNTA($C$18:C93))</f>
         <v>72</v>
@@ -4719,23 +4728,23 @@
       <c r="F93" s="34"/>
       <c r="G93" s="27"/>
     </row>
-    <row r="94" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A94" s="145" t="s">
+    <row r="94" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A94" s="192" t="s">
         <v>208</v>
       </c>
-      <c r="B94" s="145"/>
-      <c r="C94" s="145"/>
-      <c r="D94" s="145"/>
+      <c r="B94" s="192"/>
+      <c r="C94" s="192"/>
+      <c r="D94" s="192"/>
       <c r="E94" s="87"/>
       <c r="F94" s="65"/>
       <c r="G94" s="27"/>
     </row>
-    <row r="95" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A95" s="29">
         <f>IF(LEN(C95)=0,"",COUNTA($C$18:C95))</f>
         <v>73</v>
       </c>
-      <c r="B95" s="158" t="s">
+      <c r="B95" s="193" t="s">
         <v>209</v>
       </c>
       <c r="C95" s="24" t="s">
@@ -4748,12 +4757,12 @@
       <c r="F95" s="34"/>
       <c r="G95" s="27"/>
     </row>
-    <row r="96" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A96" s="29">
         <f>IF(LEN(C96)=0,"",COUNTA($C$18:C96))</f>
         <v>74</v>
       </c>
-      <c r="B96" s="159"/>
+      <c r="B96" s="194"/>
       <c r="C96" s="24" t="s">
         <v>217</v>
       </c>
@@ -4764,12 +4773,12 @@
       <c r="F96" s="34"/>
       <c r="G96" s="27"/>
     </row>
-    <row r="97" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A97" s="29">
         <f>IF(LEN(C97)=0,"",COUNTA($C$18:C97))</f>
         <v>75</v>
       </c>
-      <c r="B97" s="159"/>
+      <c r="B97" s="194"/>
       <c r="C97" s="24" t="s">
         <v>218</v>
       </c>
@@ -4780,12 +4789,12 @@
       <c r="F97" s="34"/>
       <c r="G97" s="27"/>
     </row>
-    <row r="98" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A98" s="29">
         <f>IF(LEN(C98)=0,"",COUNTA($C$18:C98))</f>
         <v>76</v>
       </c>
-      <c r="B98" s="159"/>
+      <c r="B98" s="194"/>
       <c r="C98" s="31" t="s">
         <v>219</v>
       </c>
@@ -4798,12 +4807,12 @@
       <c r="F98" s="34"/>
       <c r="G98" s="27"/>
     </row>
-    <row r="99" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A99" s="29">
         <f>IF(LEN(C99)=0,"",COUNTA($C$18:C99))</f>
         <v>77</v>
       </c>
-      <c r="B99" s="159"/>
+      <c r="B99" s="194"/>
       <c r="C99" s="31" t="s">
         <v>221</v>
       </c>
@@ -4816,7 +4825,7 @@
       <c r="F99" s="34"/>
       <c r="G99" s="27"/>
     </row>
-    <row r="100" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A100" s="29">
         <f>IF(LEN(C100)=0,"",COUNTA($C$18:C100))</f>
         <v>78</v>
@@ -4834,12 +4843,12 @@
       <c r="F100" s="34"/>
       <c r="G100" s="27"/>
     </row>
-    <row r="101" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A101" s="29">
         <f>IF(LEN(C101)=0,"",COUNTA($C$18:C101))</f>
         <v>79</v>
       </c>
-      <c r="B101" s="160" t="s">
+      <c r="B101" s="170" t="s">
         <v>225</v>
       </c>
       <c r="C101" s="24" t="s">
@@ -4854,12 +4863,12 @@
       <c r="F101" s="34"/>
       <c r="G101" s="27"/>
     </row>
-    <row r="102" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A102" s="29">
         <f>IF(LEN(C102)=0,"",COUNTA($C$18:C102))</f>
         <v>80</v>
       </c>
-      <c r="B102" s="161"/>
+      <c r="B102" s="171"/>
       <c r="C102" s="24" t="s">
         <v>230</v>
       </c>
@@ -4872,12 +4881,12 @@
       <c r="F102" s="34"/>
       <c r="G102" s="27"/>
     </row>
-    <row r="103" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A103" s="29">
         <f>IF(LEN(C103)=0,"",COUNTA($C$18:C103))</f>
         <v>81</v>
       </c>
-      <c r="B103" s="161"/>
+      <c r="B103" s="171"/>
       <c r="C103" s="24" t="s">
         <v>232</v>
       </c>
@@ -4890,12 +4899,12 @@
       <c r="F103" s="34"/>
       <c r="G103" s="27"/>
     </row>
-    <row r="104" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A104" s="29">
         <f>IF(LEN(C104)=0,"",COUNTA($C$18:C104))</f>
         <v>82</v>
       </c>
-      <c r="B104" s="161"/>
+      <c r="B104" s="171"/>
       <c r="C104" s="24" t="s">
         <v>233</v>
       </c>
@@ -4908,12 +4917,12 @@
       <c r="F104" s="68"/>
       <c r="G104" s="27"/>
     </row>
-    <row r="105" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A105" s="29">
         <f>IF(LEN(C105)=0,"",COUNTA($C$18:C105))</f>
         <v>83</v>
       </c>
-      <c r="B105" s="162"/>
+      <c r="B105" s="172"/>
       <c r="C105" s="24" t="s">
         <v>235</v>
       </c>
@@ -4924,12 +4933,12 @@
       <c r="F105" s="34"/>
       <c r="G105" s="27"/>
     </row>
-    <row r="106" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A106" s="29">
         <f>IF(LEN(C106)=0,"",COUNTA($C$18:C106))</f>
         <v>84</v>
       </c>
-      <c r="B106" s="161" t="s">
+      <c r="B106" s="171" t="s">
         <v>237</v>
       </c>
       <c r="C106" s="24" t="s">
@@ -4942,12 +4951,12 @@
       <c r="F106" s="34"/>
       <c r="G106" s="27"/>
     </row>
-    <row r="107" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A107" s="29">
         <f>IF(LEN(C107)=0,"",COUNTA($C$18:C107))</f>
         <v>85</v>
       </c>
-      <c r="B107" s="161"/>
+      <c r="B107" s="171"/>
       <c r="C107" s="24" t="s">
         <v>240</v>
       </c>
@@ -4960,12 +4969,12 @@
       <c r="F107" s="34"/>
       <c r="G107" s="27"/>
     </row>
-    <row r="108" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A108" s="29">
         <f>IF(LEN(C108)=0,"",COUNTA($C$18:C108))</f>
         <v>86</v>
       </c>
-      <c r="B108" s="161"/>
+      <c r="B108" s="171"/>
       <c r="C108" s="24" t="s">
         <v>242</v>
       </c>
@@ -4978,12 +4987,12 @@
       <c r="F108" s="34"/>
       <c r="G108" s="27"/>
     </row>
-    <row r="109" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A109" s="29">
         <f>IF(LEN(C109)=0,"",COUNTA($C$18:C109))</f>
         <v>87</v>
       </c>
-      <c r="B109" s="161"/>
+      <c r="B109" s="171"/>
       <c r="C109" s="24" t="s">
         <v>244</v>
       </c>
@@ -4996,12 +5005,12 @@
       <c r="F109" s="34"/>
       <c r="G109" s="27"/>
     </row>
-    <row r="110" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A110" s="29">
         <f>IF(LEN(C110)=0,"",COUNTA($C$18:C110))</f>
         <v>88</v>
       </c>
-      <c r="B110" s="161"/>
+      <c r="B110" s="171"/>
       <c r="C110" s="24" t="s">
         <v>246</v>
       </c>
@@ -5014,12 +5023,12 @@
       <c r="F110" s="34"/>
       <c r="G110" s="27"/>
     </row>
-    <row r="111" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A111" s="29">
         <f>IF(LEN(C111)=0,"",COUNTA($C$18:C111))</f>
         <v>89</v>
       </c>
-      <c r="B111" s="161"/>
+      <c r="B111" s="171"/>
       <c r="C111" s="24" t="s">
         <v>248</v>
       </c>
@@ -5032,12 +5041,12 @@
       <c r="F111" s="34"/>
       <c r="G111" s="27"/>
     </row>
-    <row r="112" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A112" s="29">
         <f>IF(LEN(C112)=0,"",COUNTA($C$18:C112))</f>
         <v>90</v>
       </c>
-      <c r="B112" s="161"/>
+      <c r="B112" s="171"/>
       <c r="C112" s="24" t="s">
         <v>250</v>
       </c>
@@ -5048,12 +5057,12 @@
       <c r="F112" s="34"/>
       <c r="G112" s="27"/>
     </row>
-    <row r="113" spans="1:7" ht="69" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A113" s="29">
         <f>IF(LEN(C113)=0,"",COUNTA($C$18:C113))</f>
         <v>91</v>
       </c>
-      <c r="B113" s="163" t="s">
+      <c r="B113" s="195" t="s">
         <v>251</v>
       </c>
       <c r="C113" s="24" t="s">
@@ -5070,12 +5079,12 @@
       </c>
       <c r="G113" s="90"/>
     </row>
-    <row r="114" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A114" s="29">
         <f>IF(LEN(C114)=0,"",COUNTA($C$18:C114))</f>
         <v>92</v>
       </c>
-      <c r="B114" s="163"/>
+      <c r="B114" s="195"/>
       <c r="C114" s="24" t="s">
         <v>255</v>
       </c>
@@ -5088,12 +5097,12 @@
       <c r="F114" s="34"/>
       <c r="G114" s="27"/>
     </row>
-    <row r="115" spans="1:7" ht="69" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A115" s="29">
         <f>IF(LEN(C115)=0,"",COUNTA($C$18:C115))</f>
         <v>93</v>
       </c>
-      <c r="B115" s="163"/>
+      <c r="B115" s="195"/>
       <c r="C115" s="24" t="s">
         <v>257</v>
       </c>
@@ -5108,12 +5117,12 @@
       </c>
       <c r="G115" s="90"/>
     </row>
-    <row r="116" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A116" s="29">
         <f>IF(LEN(C116)=0,"",COUNTA($C$18:C116))</f>
         <v>94</v>
       </c>
-      <c r="B116" s="163"/>
+      <c r="B116" s="195"/>
       <c r="C116" s="24" t="s">
         <v>259</v>
       </c>
@@ -5126,12 +5135,12 @@
       <c r="F116" s="34"/>
       <c r="G116" s="27"/>
     </row>
-    <row r="117" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A117" s="29">
         <f>IF(LEN(C117)=0,"",COUNTA($C$18:C117))</f>
         <v>95</v>
       </c>
-      <c r="B117" s="163"/>
+      <c r="B117" s="195"/>
       <c r="C117" s="24" t="s">
         <v>261</v>
       </c>
@@ -5144,12 +5153,12 @@
       <c r="F117" s="34"/>
       <c r="G117" s="27"/>
     </row>
-    <row r="118" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A118" s="29">
         <f>IF(LEN(C118)=0,"",COUNTA($C$18:C118))</f>
         <v>96</v>
       </c>
-      <c r="B118" s="163"/>
+      <c r="B118" s="195"/>
       <c r="C118" s="32" t="s">
         <v>263</v>
       </c>
@@ -5162,12 +5171,12 @@
       <c r="F118" s="34"/>
       <c r="G118" s="27"/>
     </row>
-    <row r="119" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A119" s="29">
         <f>IF(LEN(C119)=0,"",COUNTA($C$18:C119))</f>
         <v>97</v>
       </c>
-      <c r="B119" s="163"/>
+      <c r="B119" s="195"/>
       <c r="C119" s="24" t="s">
         <v>265</v>
       </c>
@@ -5180,12 +5189,12 @@
       <c r="F119" s="34"/>
       <c r="G119" s="27"/>
     </row>
-    <row r="120" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A120" s="29">
         <f>IF(LEN(C120)=0,"",COUNTA($C$18:C120))</f>
         <v>98</v>
       </c>
-      <c r="B120" s="163"/>
+      <c r="B120" s="195"/>
       <c r="C120" s="24" t="s">
         <v>267</v>
       </c>
@@ -5198,12 +5207,12 @@
       <c r="F120" s="34"/>
       <c r="G120" s="27"/>
     </row>
-    <row r="121" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A121" s="29">
         <f>IF(LEN(C121)=0,"",COUNTA($C$18:C121))</f>
         <v>99</v>
       </c>
-      <c r="B121" s="163"/>
+      <c r="B121" s="195"/>
       <c r="C121" s="24" t="s">
         <v>268</v>
       </c>
@@ -5216,12 +5225,12 @@
       <c r="F121" s="34"/>
       <c r="G121" s="27"/>
     </row>
-    <row r="122" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A122" s="29">
         <f>IF(LEN(C122)=0,"",COUNTA($C$18:C122))</f>
         <v>100</v>
       </c>
-      <c r="B122" s="163"/>
+      <c r="B122" s="195"/>
       <c r="C122" s="32" t="s">
         <v>270</v>
       </c>
@@ -5234,12 +5243,12 @@
       <c r="F122" s="34"/>
       <c r="G122" s="27"/>
     </row>
-    <row r="123" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A123" s="29">
         <f>IF(LEN(C123)=0,"",COUNTA($C$18:C123))</f>
         <v>101</v>
       </c>
-      <c r="B123" s="163"/>
+      <c r="B123" s="195"/>
       <c r="C123" s="24" t="s">
         <v>272</v>
       </c>
@@ -5254,12 +5263,12 @@
       </c>
       <c r="G123" s="27"/>
     </row>
-    <row r="124" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A124" s="29">
         <f>IF(LEN(C124)=0,"",COUNTA($C$18:C124))</f>
         <v>102</v>
       </c>
-      <c r="B124" s="163"/>
+      <c r="B124" s="195"/>
       <c r="C124" s="24" t="s">
         <v>275</v>
       </c>
@@ -5272,12 +5281,12 @@
       <c r="F124" s="34"/>
       <c r="G124" s="27"/>
     </row>
-    <row r="125" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A125" s="29">
         <f>IF(LEN(C125)=0,"",COUNTA($C$18:C125))</f>
         <v>103</v>
       </c>
-      <c r="B125" s="163"/>
+      <c r="B125" s="195"/>
       <c r="C125" s="24" t="s">
         <v>277</v>
       </c>
@@ -5290,12 +5299,12 @@
       <c r="F125" s="34"/>
       <c r="G125" s="27"/>
     </row>
-    <row r="126" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A126" s="29">
         <f>IF(LEN(C126)=0,"",COUNTA($C$18:C126))</f>
         <v>104</v>
       </c>
-      <c r="B126" s="163"/>
+      <c r="B126" s="195"/>
       <c r="C126" s="24" t="s">
         <v>278</v>
       </c>
@@ -5308,12 +5317,12 @@
       <c r="F126" s="34"/>
       <c r="G126" s="27"/>
     </row>
-    <row r="127" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A127" s="29">
         <f>IF(LEN(C127)=0,"",COUNTA($C$18:C127))</f>
         <v>105</v>
       </c>
-      <c r="B127" s="163"/>
+      <c r="B127" s="195"/>
       <c r="C127" s="24" t="s">
         <v>280</v>
       </c>
@@ -5326,12 +5335,12 @@
       <c r="F127" s="34"/>
       <c r="G127" s="27"/>
     </row>
-    <row r="128" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A128" s="29">
         <f>IF(LEN(C128)=0,"",COUNTA($C$18:C128))</f>
         <v>106</v>
       </c>
-      <c r="B128" s="163"/>
+      <c r="B128" s="195"/>
       <c r="C128" s="24" t="s">
         <v>281</v>
       </c>
@@ -5344,12 +5353,12 @@
       <c r="F128" s="34"/>
       <c r="G128" s="27"/>
     </row>
-    <row r="129" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A129" s="29">
         <f>IF(LEN(C129)=0,"",COUNTA($C$18:C129))</f>
         <v>107</v>
       </c>
-      <c r="B129" s="163"/>
+      <c r="B129" s="195"/>
       <c r="C129" s="24" t="s">
         <v>283</v>
       </c>
@@ -5362,12 +5371,12 @@
       <c r="F129" s="34"/>
       <c r="G129" s="27"/>
     </row>
-    <row r="130" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A130" s="29">
         <f>IF(LEN(C130)=0,"",COUNTA($C$18:C130))</f>
         <v>108</v>
       </c>
-      <c r="B130" s="163"/>
+      <c r="B130" s="195"/>
       <c r="C130" s="24" t="s">
         <v>285</v>
       </c>
@@ -5380,12 +5389,12 @@
       <c r="F130" s="34"/>
       <c r="G130" s="27"/>
     </row>
-    <row r="131" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A131" s="29">
         <f>IF(LEN(C131)=0,"",COUNTA($C$18:C131))</f>
         <v>109</v>
       </c>
-      <c r="B131" s="163"/>
+      <c r="B131" s="195"/>
       <c r="C131" s="24" t="s">
         <v>287</v>
       </c>
@@ -5398,12 +5407,12 @@
       <c r="F131" s="34"/>
       <c r="G131" s="27"/>
     </row>
-    <row r="132" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A132" s="29">
         <f>IF(LEN(C132)=0,"",COUNTA($C$18:C132))</f>
         <v>110</v>
       </c>
-      <c r="B132" s="163"/>
+      <c r="B132" s="195"/>
       <c r="C132" s="24" t="s">
         <v>289</v>
       </c>
@@ -5416,12 +5425,12 @@
       <c r="F132" s="34"/>
       <c r="G132" s="27"/>
     </row>
-    <row r="133" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A133" s="29">
         <f>IF(LEN(C133)=0,"",COUNTA($C$18:C133))</f>
         <v>111</v>
       </c>
-      <c r="B133" s="163"/>
+      <c r="B133" s="195"/>
       <c r="C133" s="24" t="s">
         <v>291</v>
       </c>
@@ -5434,12 +5443,12 @@
       <c r="F133" s="34"/>
       <c r="G133" s="27"/>
     </row>
-    <row r="134" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A134" s="29">
         <f>IF(LEN(C134)=0,"",COUNTA($C$18:C134))</f>
         <v>112</v>
       </c>
-      <c r="B134" s="163"/>
+      <c r="B134" s="195"/>
       <c r="C134" s="24" t="s">
         <v>293</v>
       </c>
@@ -5452,12 +5461,12 @@
       <c r="F134" s="34"/>
       <c r="G134" s="27"/>
     </row>
-    <row r="135" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A135" s="29">
         <f>IF(LEN(C135)=0,"",COUNTA($C$18:C135))</f>
         <v>113</v>
       </c>
-      <c r="B135" s="163"/>
+      <c r="B135" s="195"/>
       <c r="C135" s="24" t="s">
         <v>295</v>
       </c>
@@ -5470,12 +5479,12 @@
       <c r="F135" s="34"/>
       <c r="G135" s="27"/>
     </row>
-    <row r="136" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A136" s="29">
         <f>IF(LEN(C136)=0,"",COUNTA($C$18:C136))</f>
         <v>114</v>
       </c>
-      <c r="B136" s="163"/>
+      <c r="B136" s="195"/>
       <c r="C136" s="24" t="s">
         <v>297</v>
       </c>
@@ -5488,12 +5497,12 @@
       <c r="F136" s="34"/>
       <c r="G136" s="27"/>
     </row>
-    <row r="137" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A137" s="29">
         <f>IF(LEN(C137)=0,"",COUNTA($C$18:C137))</f>
         <v>115</v>
       </c>
-      <c r="B137" s="163"/>
+      <c r="B137" s="195"/>
       <c r="C137" s="24" t="s">
         <v>299</v>
       </c>
@@ -5504,12 +5513,12 @@
       <c r="F137" s="34"/>
       <c r="G137" s="27"/>
     </row>
-    <row r="138" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A138" s="29">
         <f>IF(LEN(C138)=0,"",COUNTA($C$18:C138))</f>
         <v>116</v>
       </c>
-      <c r="B138" s="163"/>
+      <c r="B138" s="195"/>
       <c r="C138" s="24" t="s">
         <v>300</v>
       </c>
@@ -5520,12 +5529,12 @@
       <c r="F138" s="34"/>
       <c r="G138" s="27"/>
     </row>
-    <row r="139" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A139" s="29">
         <f>IF(LEN(C139)=0,"",COUNTA($C$18:C139))</f>
         <v>117</v>
       </c>
-      <c r="B139" s="163"/>
+      <c r="B139" s="195"/>
       <c r="C139" s="24" t="s">
         <v>301</v>
       </c>
@@ -5538,12 +5547,12 @@
       <c r="F139" s="34"/>
       <c r="G139" s="27"/>
     </row>
-    <row r="140" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A140" s="29">
         <f>IF(LEN(C140)=0,"",COUNTA($C$18:C140))</f>
         <v>118</v>
       </c>
-      <c r="B140" s="163"/>
+      <c r="B140" s="195"/>
       <c r="C140" s="24" t="s">
         <v>303</v>
       </c>
@@ -5556,12 +5565,12 @@
       <c r="F140" s="34"/>
       <c r="G140" s="27"/>
     </row>
-    <row r="141" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A141" s="29">
         <f>IF(LEN(C141)=0,"",COUNTA($C$18:C141))</f>
         <v>119</v>
       </c>
-      <c r="B141" s="163"/>
+      <c r="B141" s="195"/>
       <c r="C141" s="24" t="s">
         <v>305</v>
       </c>
@@ -5574,12 +5583,12 @@
       <c r="F141" s="34"/>
       <c r="G141" s="27"/>
     </row>
-    <row r="142" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A142" s="29">
         <f>IF(LEN(C142)=0,"",COUNTA($C$18:C142))</f>
         <v>120</v>
       </c>
-      <c r="B142" s="163"/>
+      <c r="B142" s="195"/>
       <c r="C142" s="24" t="s">
         <v>307</v>
       </c>
@@ -5592,18 +5601,18 @@
       <c r="F142" s="34"/>
       <c r="G142" s="27"/>
     </row>
-    <row r="143" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A143" s="145" t="s">
+    <row r="143" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A143" s="192" t="s">
         <v>309</v>
       </c>
-      <c r="B143" s="145"/>
-      <c r="C143" s="145"/>
-      <c r="D143" s="145"/>
+      <c r="B143" s="192"/>
+      <c r="C143" s="192"/>
+      <c r="D143" s="192"/>
       <c r="E143" s="87"/>
       <c r="F143" s="65"/>
       <c r="G143" s="27"/>
     </row>
-    <row r="144" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A144" s="29">
         <f>IF(LEN(C144)=0,"",COUNTA($C$18:C144))</f>
         <v>121</v>
@@ -5621,7 +5630,7 @@
       <c r="F144" s="34"/>
       <c r="G144" s="27"/>
     </row>
-    <row r="145" spans="1:8" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A145" s="29">
         <f>IF(LEN(C145)=0,"",COUNTA($C$18:C145))</f>
         <v>122</v>
@@ -5640,17 +5649,17 @@
       <c r="G145" s="27"/>
       <c r="H145" s="27"/>
     </row>
-    <row r="148" spans="1:8" s="97" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A148" s="147" t="s">
+    <row r="148" spans="1:8" s="97" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A148" s="188" t="s">
         <v>321</v>
       </c>
-      <c r="B148" s="148"/>
-      <c r="C148" s="148"/>
-      <c r="D148" s="149"/>
+      <c r="B148" s="189"/>
+      <c r="C148" s="189"/>
+      <c r="D148" s="190"/>
       <c r="E148" s="96"/>
       <c r="F148" s="60"/>
     </row>
-    <row r="149" spans="1:8" s="97" customFormat="1" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" s="97" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A149" s="29">
         <f>IF(LEN(C149)=0,"",COUNTA($C$18:C149))</f>
         <v>123</v>
@@ -5665,11 +5674,11 @@
       <c r="E149" s="100">
         <v>71000</v>
       </c>
-      <c r="F149" s="150" t="s">
+      <c r="F149" s="197" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="150" spans="1:8" s="97" customFormat="1" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" s="97" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A150" s="29">
         <f>IF(LEN(C150)=0,"",COUNTA($C$18:C150))</f>
         <v>124</v>
@@ -5684,20 +5693,20 @@
       <c r="E150" s="100">
         <v>86000</v>
       </c>
-      <c r="F150" s="151"/>
-    </row>
-    <row r="151" spans="1:8" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A151" s="145" t="s">
+      <c r="F150" s="198"/>
+    </row>
+    <row r="151" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A151" s="192" t="s">
         <v>327</v>
       </c>
-      <c r="B151" s="145"/>
-      <c r="C151" s="145"/>
-      <c r="D151" s="145"/>
+      <c r="B151" s="192"/>
+      <c r="C151" s="192"/>
+      <c r="D151" s="192"/>
       <c r="E151" s="87"/>
       <c r="F151" s="65"/>
       <c r="G151" s="27"/>
     </row>
-    <row r="152" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="29">
         <f>IF(LEN(C152)=0,"",COUNTA($C$18:C152))</f>
         <v>125</v>
@@ -5712,12 +5721,12 @@
       <c r="E152" s="79">
         <v>1968000</v>
       </c>
-      <c r="F152" s="152" t="s">
+      <c r="F152" s="173" t="s">
         <v>330</v>
       </c>
       <c r="G152" s="27"/>
     </row>
-    <row r="153" spans="1:8" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A153" s="29">
         <f>IF(LEN(C153)=0,"",COUNTA($C$18:C153))</f>
         <v>126</v>
@@ -5732,10 +5741,10 @@
       <c r="E153" s="79">
         <v>2952000</v>
       </c>
-      <c r="F153" s="153"/>
+      <c r="F153" s="174"/>
       <c r="G153" s="27"/>
     </row>
-    <row r="154" spans="1:8" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" ht="66" x14ac:dyDescent="0.25">
       <c r="A154" s="29">
         <f>IF(LEN(C154)=0,"",COUNTA($C$18:C154))</f>
         <v>127</v>
@@ -5750,10 +5759,10 @@
       <c r="E154" s="79">
         <v>4100000</v>
       </c>
-      <c r="F154" s="154"/>
+      <c r="F154" s="175"/>
       <c r="G154" s="27"/>
     </row>
-    <row r="155" spans="1:8" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A155" s="29">
         <f>IF(LEN(C155)=0,"",COUNTA($C$18:C155))</f>
         <v>128</v>
@@ -5771,7 +5780,7 @@
       <c r="F155" s="84"/>
       <c r="G155" s="27"/>
     </row>
-    <row r="156" spans="1:8" ht="160.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8" ht="160.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="29">
         <f>IF(LEN(C156)=0,"",COUNTA($C$18:C156))</f>
         <v>129</v>
@@ -5791,7 +5800,7 @@
       </c>
       <c r="G156" s="27"/>
     </row>
-    <row r="157" spans="1:8" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A157" s="29">
         <f>IF(LEN(C157)=0,"",COUNTA($C$18:C157))</f>
         <v>130</v>
@@ -5809,7 +5818,7 @@
       <c r="F157" s="34"/>
       <c r="G157" s="27"/>
     </row>
-    <row r="158" spans="1:8" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A158" s="29">
         <f>IF(LEN(C158)=0,"",COUNTA($C$18:C158))</f>
         <v>131</v>
@@ -5827,7 +5836,7 @@
       <c r="F158" s="34"/>
       <c r="G158" s="27"/>
     </row>
-    <row r="159" spans="1:8" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A159" s="29">
         <f>IF(LEN(C159)=0,"",COUNTA($C$18:C159))</f>
         <v>132</v>
@@ -5845,18 +5854,18 @@
       <c r="F159" s="34"/>
       <c r="G159" s="27"/>
     </row>
-    <row r="160" spans="1:8" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A160" s="145" t="s">
+    <row r="160" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A160" s="192" t="s">
         <v>346</v>
       </c>
-      <c r="B160" s="145"/>
-      <c r="C160" s="145"/>
-      <c r="D160" s="145"/>
+      <c r="B160" s="192"/>
+      <c r="C160" s="192"/>
+      <c r="D160" s="192"/>
       <c r="E160" s="87"/>
       <c r="F160" s="65"/>
       <c r="G160" s="27"/>
     </row>
-    <row r="161" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A161" s="29">
         <f>IF(LEN(C161)=0,"",COUNTA($C$18:C161))</f>
         <v>133</v>
@@ -5874,18 +5883,18 @@
       <c r="F161" s="34"/>
       <c r="G161" s="27"/>
     </row>
-    <row r="162" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A162" s="145" t="s">
+    <row r="162" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A162" s="192" t="s">
         <v>349</v>
       </c>
-      <c r="B162" s="145"/>
-      <c r="C162" s="145"/>
-      <c r="D162" s="145"/>
+      <c r="B162" s="192"/>
+      <c r="C162" s="192"/>
+      <c r="D162" s="192"/>
       <c r="E162" s="87"/>
       <c r="F162" s="65"/>
       <c r="G162" s="27"/>
     </row>
-    <row r="163" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A163" s="29">
         <f>IF(LEN(C163)=0,"",COUNTA($C$18:C163))</f>
         <v>134</v>
@@ -5903,7 +5912,7 @@
       <c r="F163" s="34"/>
       <c r="G163" s="27"/>
     </row>
-    <row r="164" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A164" s="29">
         <f>IF(LEN(C164)=0,"",COUNTA($C$18:C164))</f>
         <v>135</v>
@@ -5921,7 +5930,7 @@
       <c r="F164" s="34"/>
       <c r="G164" s="27"/>
     </row>
-    <row r="165" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A165" s="29">
         <f>IF(LEN(C165)=0,"",COUNTA($C$18:C165))</f>
         <v>136</v>
@@ -5939,7 +5948,7 @@
       <c r="F165" s="34"/>
       <c r="G165" s="27"/>
     </row>
-    <row r="166" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A166" s="29">
         <f>IF(LEN(C166)=0,"",COUNTA($C$18:C166))</f>
         <v>137</v>
@@ -5957,7 +5966,7 @@
       <c r="F166" s="34"/>
       <c r="G166" s="27"/>
     </row>
-    <row r="167" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A167" s="29">
         <f>IF(LEN(C167)=0,"",COUNTA($C$18:C167))</f>
         <v>138</v>
@@ -5975,7 +5984,7 @@
       <c r="F167" s="34"/>
       <c r="G167" s="27"/>
     </row>
-    <row r="168" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A168" s="29">
         <f>IF(LEN(C168)=0,"",COUNTA($C$18:C168))</f>
         <v>139</v>
@@ -5993,7 +6002,7 @@
       <c r="F168" s="34"/>
       <c r="G168" s="27"/>
     </row>
-    <row r="169" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A169" s="29">
         <f>IF(LEN(C169)=0,"",COUNTA($C$18:C169))</f>
         <v>140</v>
@@ -6011,7 +6020,7 @@
       <c r="F169" s="34"/>
       <c r="G169" s="27"/>
     </row>
-    <row r="170" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A170" s="29">
         <f>IF(LEN(C170)=0,"",COUNTA($C$18:C170))</f>
         <v>141</v>
@@ -6029,18 +6038,18 @@
       <c r="F170" s="34"/>
       <c r="G170" s="27"/>
     </row>
-    <row r="171" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A171" s="147" t="s">
+    <row r="171" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A171" s="188" t="s">
         <v>369</v>
       </c>
-      <c r="B171" s="148"/>
-      <c r="C171" s="148"/>
-      <c r="D171" s="149"/>
+      <c r="B171" s="189"/>
+      <c r="C171" s="189"/>
+      <c r="D171" s="190"/>
       <c r="E171" s="64"/>
       <c r="F171" s="65"/>
       <c r="G171" s="27"/>
     </row>
-    <row r="172" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A172" s="29">
         <f>IF(LEN(C172)=0,"",COUNTA($C$18:C172))</f>
         <v>142</v>
@@ -6056,7 +6065,7 @@
       <c r="F172" s="34"/>
       <c r="G172" s="27"/>
     </row>
-    <row r="173" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A173" s="29">
         <f>IF(LEN(C173)=0,"",COUNTA($C$18:C173))</f>
         <v>143</v>
@@ -6074,7 +6083,7 @@
       <c r="F173" s="34"/>
       <c r="G173" s="27"/>
     </row>
-    <row r="174" spans="1:7" ht="134.4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" ht="132" x14ac:dyDescent="0.25">
       <c r="A174" s="29">
         <f>IF(LEN(C174)=0,"",COUNTA($C$18:C174))</f>
         <v>144</v>
@@ -6092,7 +6101,7 @@
       <c r="F174" s="34"/>
       <c r="G174" s="27"/>
     </row>
-    <row r="175" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" ht="99" x14ac:dyDescent="0.25">
       <c r="A175" s="29">
         <f>IF(LEN(C175)=0,"",COUNTA($C$18:C175))</f>
         <v>145</v>
@@ -6110,7 +6119,7 @@
       <c r="F175" s="34"/>
       <c r="G175" s="27"/>
     </row>
-    <row r="176" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A176" s="29">
         <f>IF(LEN(C176)=0,"",COUNTA($C$18:C176))</f>
         <v>146</v>
@@ -6128,18 +6137,18 @@
       <c r="F176" s="34"/>
       <c r="G176" s="27"/>
     </row>
-    <row r="177" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A177" s="147" t="s">
+    <row r="177" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A177" s="188" t="s">
         <v>379</v>
       </c>
-      <c r="B177" s="148"/>
-      <c r="C177" s="148"/>
-      <c r="D177" s="149"/>
+      <c r="B177" s="189"/>
+      <c r="C177" s="189"/>
+      <c r="D177" s="190"/>
       <c r="E177" s="64"/>
       <c r="F177" s="65"/>
       <c r="G177" s="27"/>
     </row>
-    <row r="178" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A178" s="29">
         <f>IF(LEN(C178)=0,"",COUNTA($C$18:C178))</f>
         <v>147</v>
@@ -6157,7 +6166,7 @@
       <c r="F178" s="34"/>
       <c r="G178" s="27"/>
     </row>
-    <row r="179" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A179" s="29">
         <f>IF(LEN(C179)=0,"",COUNTA($C$18:C179))</f>
         <v>148</v>
@@ -6175,7 +6184,7 @@
       <c r="F179" s="34"/>
       <c r="G179" s="27"/>
     </row>
-    <row r="180" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A180" s="29">
         <f>IF(LEN(C180)=0,"",COUNTA($C$18:C180))</f>
         <v>149</v>
@@ -6193,18 +6202,18 @@
       <c r="F180" s="34"/>
       <c r="G180" s="27"/>
     </row>
-    <row r="181" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A181" s="147" t="s">
+    <row r="181" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A181" s="188" t="s">
         <v>386</v>
       </c>
-      <c r="B181" s="148"/>
-      <c r="C181" s="148"/>
-      <c r="D181" s="149"/>
+      <c r="B181" s="189"/>
+      <c r="C181" s="189"/>
+      <c r="D181" s="190"/>
       <c r="E181" s="64"/>
       <c r="F181" s="65"/>
       <c r="G181" s="27"/>
     </row>
-    <row r="182" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A182" s="29">
         <f>IF(LEN(C182)=0,"",COUNTA($C$18:C182))</f>
         <v>150</v>
@@ -6214,13 +6223,13 @@
         <v>387</v>
       </c>
       <c r="D182" s="24"/>
-      <c r="E182" s="155">
+      <c r="E182" s="199">
         <v>183000</v>
       </c>
       <c r="F182" s="34"/>
       <c r="G182" s="27"/>
     </row>
-    <row r="183" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A183" s="29">
         <f>IF(LEN(C183)=0,"",COUNTA($C$18:C183))</f>
         <v>151</v>
@@ -6230,11 +6239,11 @@
         <v>388</v>
       </c>
       <c r="D183" s="24"/>
-      <c r="E183" s="156"/>
+      <c r="E183" s="200"/>
       <c r="F183" s="34"/>
       <c r="G183" s="27"/>
     </row>
-    <row r="184" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A184" s="29">
         <f>IF(LEN(C184)=0,"",COUNTA($C$18:C184))</f>
         <v>152</v>
@@ -6244,11 +6253,11 @@
         <v>389</v>
       </c>
       <c r="D184" s="24"/>
-      <c r="E184" s="156"/>
+      <c r="E184" s="200"/>
       <c r="F184" s="34"/>
       <c r="G184" s="27"/>
     </row>
-    <row r="185" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A185" s="29">
         <f>IF(LEN(C185)=0,"",COUNTA($C$18:C185))</f>
         <v>153</v>
@@ -6258,22 +6267,22 @@
         <v>390</v>
       </c>
       <c r="D185" s="24"/>
-      <c r="E185" s="157"/>
+      <c r="E185" s="201"/>
       <c r="F185" s="34"/>
       <c r="G185" s="27"/>
     </row>
-    <row r="186" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A186" s="147" t="s">
+    <row r="186" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A186" s="188" t="s">
         <v>391</v>
       </c>
-      <c r="B186" s="148"/>
-      <c r="C186" s="148"/>
-      <c r="D186" s="149"/>
+      <c r="B186" s="189"/>
+      <c r="C186" s="189"/>
+      <c r="D186" s="190"/>
       <c r="E186" s="64"/>
       <c r="F186" s="65"/>
       <c r="G186" s="27"/>
     </row>
-    <row r="187" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A187" s="29">
         <f>IF(LEN(C187)=0,"",COUNTA($C$18:C187))</f>
         <v>154</v>
@@ -6289,7 +6298,7 @@
       <c r="F187" s="34"/>
       <c r="G187" s="27"/>
     </row>
-    <row r="188" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A188" s="29">
         <f>IF(LEN(C188)=0,"",COUNTA($C$18:C188))</f>
         <v>155</v>
@@ -6305,7 +6314,7 @@
       <c r="F188" s="34"/>
       <c r="G188" s="27"/>
     </row>
-    <row r="189" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A189" s="29">
         <f>IF(LEN(C189)=0,"",COUNTA($C$18:C189))</f>
         <v>156</v>
@@ -6321,7 +6330,7 @@
       <c r="F189" s="34"/>
       <c r="G189" s="27"/>
     </row>
-    <row r="190" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A190" s="29">
         <f>IF(LEN(C190)=0,"",COUNTA($C$18:C190))</f>
         <v>157</v>
@@ -6337,7 +6346,7 @@
       <c r="F190" s="34"/>
       <c r="G190" s="27"/>
     </row>
-    <row r="191" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A191" s="105"/>
       <c r="B191" s="106"/>
       <c r="C191" s="105"/>
@@ -6345,67 +6354,67 @@
       <c r="E191" s="107"/>
       <c r="F191" s="108"/>
     </row>
-    <row r="192" spans="1:7" s="110" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A192" s="146" t="s">
+    <row r="192" spans="1:7" s="110" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A192" s="196" t="s">
         <v>396</v>
       </c>
-      <c r="B192" s="146"/>
-      <c r="C192" s="146"/>
-      <c r="D192" s="146"/>
+      <c r="B192" s="196"/>
+      <c r="C192" s="196"/>
+      <c r="D192" s="196"/>
       <c r="E192" s="7"/>
       <c r="F192" s="109"/>
     </row>
-    <row r="193" spans="1:6" s="110" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" s="110" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A193" s="111"/>
-      <c r="B193" s="143" t="s">
+      <c r="B193" s="202" t="s">
         <v>397</v>
       </c>
-      <c r="C193" s="143"/>
-      <c r="D193" s="143"/>
-      <c r="E193" s="143"/>
-      <c r="F193" s="143"/>
-    </row>
-    <row r="194" spans="1:6" s="110" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="C193" s="202"/>
+      <c r="D193" s="202"/>
+      <c r="E193" s="202"/>
+      <c r="F193" s="202"/>
+    </row>
+    <row r="194" spans="1:6" s="110" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A194" s="111"/>
-      <c r="B194" s="143" t="s">
+      <c r="B194" s="202" t="s">
         <v>398</v>
       </c>
-      <c r="C194" s="143"/>
-      <c r="D194" s="143"/>
-      <c r="E194" s="143"/>
-      <c r="F194" s="143"/>
-    </row>
-    <row r="195" spans="1:6" s="113" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C194" s="202"/>
+      <c r="D194" s="202"/>
+      <c r="E194" s="202"/>
+      <c r="F194" s="202"/>
+    </row>
+    <row r="195" spans="1:6" s="113" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="112"/>
-      <c r="B195" s="143" t="s">
+      <c r="B195" s="202" t="s">
         <v>399</v>
       </c>
-      <c r="C195" s="143"/>
-      <c r="D195" s="143"/>
-      <c r="E195" s="143"/>
-      <c r="F195" s="143"/>
-    </row>
-    <row r="196" spans="1:6" s="115" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C195" s="202"/>
+      <c r="D195" s="202"/>
+      <c r="E195" s="202"/>
+      <c r="F195" s="202"/>
+    </row>
+    <row r="196" spans="1:6" s="115" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="114"/>
-      <c r="B196" s="144" t="s">
+      <c r="B196" s="203" t="s">
         <v>400</v>
       </c>
-      <c r="C196" s="144"/>
-      <c r="D196" s="144"/>
-      <c r="E196" s="144"/>
-      <c r="F196" s="144"/>
-    </row>
-    <row r="197" spans="1:6" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C196" s="203"/>
+      <c r="D196" s="203"/>
+      <c r="E196" s="203"/>
+      <c r="F196" s="203"/>
+    </row>
+    <row r="197" spans="1:6" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="109"/>
-      <c r="B197" s="143" t="s">
+      <c r="B197" s="202" t="s">
         <v>401</v>
       </c>
-      <c r="C197" s="143"/>
-      <c r="D197" s="143"/>
-      <c r="E197" s="143"/>
-      <c r="F197" s="143"/>
-    </row>
-    <row r="198" spans="1:6" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="C197" s="202"/>
+      <c r="D197" s="202"/>
+      <c r="E197" s="202"/>
+      <c r="F197" s="202"/>
+    </row>
+    <row r="198" spans="1:6" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A198" s="109"/>
       <c r="B198" s="112" t="s">
         <v>402</v>
@@ -6415,7 +6424,7 @@
       <c r="E198" s="7"/>
       <c r="F198" s="5"/>
     </row>
-    <row r="199" spans="1:6" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A199" s="109"/>
       <c r="B199" s="112" t="s">
         <v>403</v>
@@ -6425,7 +6434,7 @@
       <c r="E199" s="7"/>
       <c r="F199" s="5"/>
     </row>
-    <row r="200" spans="1:6" s="121" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6" s="121" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A200" s="117" t="s">
         <v>404</v>
       </c>
@@ -6435,7 +6444,7 @@
       <c r="E200" s="119"/>
       <c r="F200" s="120"/>
     </row>
-    <row r="201" spans="1:6" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A201" s="109"/>
       <c r="B201" s="5" t="s">
         <v>405</v>
@@ -6447,7 +6456,7 @@
       <c r="E201" s="10"/>
       <c r="F201" s="5"/>
     </row>
-    <row r="202" spans="1:6" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A202" s="109"/>
       <c r="B202" s="5" t="s">
         <v>407</v>
@@ -6457,7 +6466,7 @@
       <c r="E202" s="10"/>
       <c r="F202" s="5"/>
     </row>
-    <row r="203" spans="1:6" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A203" s="109"/>
       <c r="B203" s="5" t="s">
         <v>408</v>
@@ -6469,39 +6478,11 @@
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="D1:F5"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="A10:F11"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="F24:F26"/>
-    <mergeCell ref="B27:B30"/>
-    <mergeCell ref="F28:F30"/>
-    <mergeCell ref="B68:B70"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="B38:B50"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="D51:D53"/>
-    <mergeCell ref="F51:F53"/>
-    <mergeCell ref="B54:B57"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="B59:B65"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="A71:D71"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="B77:B90"/>
-    <mergeCell ref="A91:D91"/>
-    <mergeCell ref="A94:D94"/>
-    <mergeCell ref="B95:B99"/>
-    <mergeCell ref="B101:B105"/>
-    <mergeCell ref="B106:B112"/>
-    <mergeCell ref="B113:B142"/>
+    <mergeCell ref="B193:F193"/>
+    <mergeCell ref="B194:F194"/>
+    <mergeCell ref="B195:F195"/>
+    <mergeCell ref="B196:F196"/>
+    <mergeCell ref="B197:F197"/>
     <mergeCell ref="A143:D143"/>
     <mergeCell ref="A192:D192"/>
     <mergeCell ref="A148:D148"/>
@@ -6515,11 +6496,39 @@
     <mergeCell ref="A181:D181"/>
     <mergeCell ref="E182:E185"/>
     <mergeCell ref="A186:D186"/>
-    <mergeCell ref="B193:F193"/>
-    <mergeCell ref="B194:F194"/>
-    <mergeCell ref="B195:F195"/>
-    <mergeCell ref="B196:F196"/>
-    <mergeCell ref="B197:F197"/>
+    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="B95:B99"/>
+    <mergeCell ref="B101:B105"/>
+    <mergeCell ref="B106:B112"/>
+    <mergeCell ref="B113:B142"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="B77:B90"/>
+    <mergeCell ref="A91:D91"/>
+    <mergeCell ref="B68:B70"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="B38:B50"/>
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="D51:D53"/>
+    <mergeCell ref="F51:F53"/>
+    <mergeCell ref="B54:B57"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="B59:B65"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="D1:F5"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="A10:F11"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="F28:F30"/>
   </mergeCells>
   <pageMargins left="0.35433070866141736" right="0.15748031496062992" top="0.23622047244094491" bottom="0.19685039370078741" header="0.15748031496062992" footer="0.15748031496062992"/>
   <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -6543,83 +6552,83 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O63"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="19" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" style="122" customWidth="1"/>
-    <col min="3" max="3" width="53.33203125" style="19" customWidth="1"/>
-    <col min="4" max="4" width="48.5546875" style="19" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="122" customWidth="1"/>
+    <col min="3" max="3" width="53.28515625" style="19" customWidth="1"/>
+    <col min="4" max="4" width="48.5703125" style="19" customWidth="1"/>
     <col min="5" max="5" width="13" style="123" customWidth="1"/>
-    <col min="6" max="9" width="17.88671875" style="123" customWidth="1"/>
-    <col min="10" max="10" width="28.33203125" style="124" customWidth="1"/>
-    <col min="11" max="11" width="19.6640625" style="19" customWidth="1"/>
-    <col min="12" max="12" width="9.88671875" style="19" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.109375" style="19"/>
+    <col min="6" max="9" width="17.85546875" style="123" customWidth="1"/>
+    <col min="10" max="10" width="28.28515625" style="124" customWidth="1"/>
+    <col min="11" max="11" width="19.7109375" style="19" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" style="19" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="181" t="s">
+      <c r="D1" s="150" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="182"/>
-      <c r="F1" s="182"/>
-      <c r="G1" s="182"/>
-      <c r="H1" s="182"/>
-      <c r="I1" s="182"/>
-      <c r="J1" s="183"/>
-    </row>
-    <row r="2" spans="1:15" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E1" s="151"/>
+      <c r="F1" s="151"/>
+      <c r="G1" s="151"/>
+      <c r="H1" s="151"/>
+      <c r="I1" s="151"/>
+      <c r="J1" s="152"/>
+    </row>
+    <row r="2" spans="1:15" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="181"/>
-      <c r="E2" s="182"/>
-      <c r="F2" s="182"/>
-      <c r="G2" s="182"/>
-      <c r="H2" s="182"/>
-      <c r="I2" s="182"/>
-      <c r="J2" s="183"/>
-    </row>
-    <row r="3" spans="1:15" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D2" s="150"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="151"/>
+      <c r="G2" s="151"/>
+      <c r="H2" s="151"/>
+      <c r="I2" s="151"/>
+      <c r="J2" s="152"/>
+    </row>
+    <row r="3" spans="1:15" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="181"/>
-      <c r="E3" s="182"/>
-      <c r="F3" s="182"/>
-      <c r="G3" s="182"/>
-      <c r="H3" s="182"/>
-      <c r="I3" s="182"/>
-      <c r="J3" s="183"/>
-    </row>
-    <row r="4" spans="1:15" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D3" s="150"/>
+      <c r="E3" s="151"/>
+      <c r="F3" s="151"/>
+      <c r="G3" s="151"/>
+      <c r="H3" s="151"/>
+      <c r="I3" s="151"/>
+      <c r="J3" s="152"/>
+    </row>
+    <row r="4" spans="1:15" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="181"/>
-      <c r="E4" s="182"/>
-      <c r="F4" s="182"/>
-      <c r="G4" s="182"/>
-      <c r="H4" s="182"/>
-      <c r="I4" s="182"/>
-      <c r="J4" s="183"/>
-    </row>
-    <row r="5" spans="1:15" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D4" s="150"/>
+      <c r="E4" s="151"/>
+      <c r="F4" s="151"/>
+      <c r="G4" s="151"/>
+      <c r="H4" s="151"/>
+      <c r="I4" s="151"/>
+      <c r="J4" s="152"/>
+    </row>
+    <row r="5" spans="1:15" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="184"/>
-      <c r="E5" s="185"/>
-      <c r="F5" s="185"/>
-      <c r="G5" s="185"/>
-      <c r="H5" s="185"/>
-      <c r="I5" s="185"/>
-      <c r="J5" s="186"/>
-    </row>
-    <row r="6" spans="1:15" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="D5" s="153"/>
+      <c r="E5" s="154"/>
+      <c r="F5" s="154"/>
+      <c r="G5" s="154"/>
+      <c r="H5" s="154"/>
+      <c r="I5" s="154"/>
+      <c r="J5" s="155"/>
+    </row>
+    <row r="6" spans="1:15" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -6631,26 +6640,26 @@
       <c r="I6" s="7"/>
       <c r="J6" s="5"/>
     </row>
-    <row r="7" spans="1:15" s="4" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A7" s="187" t="s">
+    <row r="7" spans="1:15" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="156" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="188"/>
-      <c r="C7" s="188"/>
-      <c r="D7" s="188"/>
-      <c r="E7" s="188"/>
-      <c r="F7" s="188"/>
-      <c r="G7" s="188"/>
-      <c r="H7" s="188"/>
-      <c r="I7" s="188"/>
-      <c r="J7" s="189"/>
+      <c r="B7" s="157"/>
+      <c r="C7" s="157"/>
+      <c r="D7" s="157"/>
+      <c r="E7" s="157"/>
+      <c r="F7" s="157"/>
+      <c r="G7" s="157"/>
+      <c r="H7" s="157"/>
+      <c r="I7" s="157"/>
+      <c r="J7" s="158"/>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
     </row>
-    <row r="8" spans="1:15" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -6667,61 +6676,61 @@
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
     </row>
-    <row r="9" spans="1:15" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
-      <c r="B9" s="190" t="s">
+      <c r="B9" s="159" t="s">
         <v>409</v>
       </c>
-      <c r="C9" s="191"/>
-      <c r="D9" s="191"/>
-      <c r="E9" s="191"/>
-      <c r="F9" s="191"/>
-      <c r="G9" s="191"/>
-      <c r="H9" s="191"/>
-      <c r="I9" s="191"/>
-      <c r="J9" s="192"/>
+      <c r="C9" s="160"/>
+      <c r="D9" s="160"/>
+      <c r="E9" s="160"/>
+      <c r="F9" s="160"/>
+      <c r="G9" s="160"/>
+      <c r="H9" s="160"/>
+      <c r="I9" s="160"/>
+      <c r="J9" s="161"/>
       <c r="K9" s="12"/>
       <c r="L9" s="12"/>
       <c r="M9" s="12"/>
       <c r="N9" s="12"/>
     </row>
-    <row r="10" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="193" t="s">
+    <row r="10" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="162" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="194"/>
-      <c r="C10" s="194"/>
-      <c r="D10" s="194"/>
-      <c r="E10" s="194"/>
-      <c r="F10" s="194"/>
-      <c r="G10" s="194"/>
-      <c r="H10" s="194"/>
-      <c r="I10" s="194"/>
-      <c r="J10" s="195"/>
+      <c r="B10" s="163"/>
+      <c r="C10" s="163"/>
+      <c r="D10" s="163"/>
+      <c r="E10" s="163"/>
+      <c r="F10" s="163"/>
+      <c r="G10" s="163"/>
+      <c r="H10" s="163"/>
+      <c r="I10" s="163"/>
+      <c r="J10" s="164"/>
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
       <c r="M10" s="13"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13"/>
     </row>
-    <row r="11" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="196"/>
-      <c r="B11" s="197"/>
-      <c r="C11" s="197"/>
-      <c r="D11" s="197"/>
-      <c r="E11" s="197"/>
-      <c r="F11" s="197"/>
-      <c r="G11" s="197"/>
-      <c r="H11" s="197"/>
-      <c r="I11" s="197"/>
-      <c r="J11" s="198"/>
+    <row r="11" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="165"/>
+      <c r="B11" s="166"/>
+      <c r="C11" s="166"/>
+      <c r="D11" s="166"/>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="166"/>
+      <c r="H11" s="166"/>
+      <c r="I11" s="166"/>
+      <c r="J11" s="167"/>
       <c r="K11" s="14"/>
       <c r="L11" s="14"/>
       <c r="M11" s="14"/>
       <c r="N11" s="14"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="1:15" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="15"/>
@@ -6733,7 +6742,7 @@
       <c r="I12" s="17"/>
       <c r="J12" s="134"/>
     </row>
-    <row r="13" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>3</v>
       </c>
@@ -6744,26 +6753,26 @@
       <c r="D13" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="E13" s="224" t="s">
+      <c r="E13" s="212" t="s">
         <v>428</v>
       </c>
-      <c r="F13" s="221" t="s">
+      <c r="F13" s="209" t="s">
         <v>6</v>
       </c>
-      <c r="G13" s="222"/>
-      <c r="H13" s="222"/>
-      <c r="I13" s="223"/>
+      <c r="G13" s="210"/>
+      <c r="H13" s="210"/>
+      <c r="I13" s="211"/>
       <c r="J13" s="22" t="s">
         <v>7</v>
       </c>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" spans="1:15" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="33" x14ac:dyDescent="0.25">
       <c r="A14" s="20"/>
       <c r="B14" s="137"/>
       <c r="C14" s="138"/>
       <c r="D14" s="20"/>
-      <c r="E14" s="225"/>
+      <c r="E14" s="213"/>
       <c r="F14" s="139" t="s">
         <v>424</v>
       </c>
@@ -6779,14 +6788,14 @@
       <c r="J14" s="140"/>
       <c r="K14" s="126"/>
     </row>
-    <row r="15" spans="1:15" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A15" s="127" t="s">
         <v>411</v>
       </c>
-      <c r="B15" s="202" t="s">
+      <c r="B15" s="216" t="s">
         <v>412</v>
       </c>
-      <c r="C15" s="203"/>
+      <c r="C15" s="217"/>
       <c r="D15" s="128"/>
       <c r="E15" s="135" t="s">
         <v>413</v>
@@ -6806,14 +6815,14 @@
       <c r="J15" s="130"/>
       <c r="K15" s="126"/>
     </row>
-    <row r="16" spans="1:15" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="127" t="s">
         <v>414</v>
       </c>
-      <c r="B16" s="202" t="s">
+      <c r="B16" s="216" t="s">
         <v>415</v>
       </c>
-      <c r="C16" s="203"/>
+      <c r="C16" s="217"/>
       <c r="D16" s="128"/>
       <c r="E16" s="129"/>
       <c r="F16" s="129"/>
@@ -6823,117 +6832,117 @@
       <c r="J16" s="130"/>
       <c r="K16" s="126"/>
     </row>
-    <row r="17" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="209">
+    <row r="17" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="219">
         <f>IF(LEN(C17)=0,"",COUNTA($C$17:C17))</f>
         <v>1</v>
       </c>
-      <c r="B17" s="160" t="s">
+      <c r="B17" s="170" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="212" t="s">
+      <c r="C17" s="222" t="s">
         <v>9</v>
       </c>
       <c r="D17" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="155">
+      <c r="E17" s="199">
         <v>120000</v>
       </c>
-      <c r="F17" s="155">
+      <c r="F17" s="199">
         <v>120000</v>
       </c>
-      <c r="G17" s="155">
+      <c r="G17" s="199">
         <f>E17</f>
         <v>120000</v>
       </c>
-      <c r="H17" s="155">
+      <c r="H17" s="199">
         <f>E17</f>
         <v>120000</v>
       </c>
-      <c r="I17" s="155">
+      <c r="I17" s="199">
         <f>E17</f>
         <v>120000</v>
       </c>
-      <c r="J17" s="206"/>
+      <c r="J17" s="226"/>
       <c r="K17" s="26"/>
     </row>
-    <row r="18" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="210"/>
-      <c r="B18" s="161"/>
-      <c r="C18" s="213"/>
+    <row r="18" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="220"/>
+      <c r="B18" s="171"/>
+      <c r="C18" s="223"/>
       <c r="D18" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E18" s="156"/>
-      <c r="F18" s="156"/>
-      <c r="G18" s="156"/>
-      <c r="H18" s="156"/>
-      <c r="I18" s="156"/>
-      <c r="J18" s="207"/>
+      <c r="E18" s="200"/>
+      <c r="F18" s="200"/>
+      <c r="G18" s="200"/>
+      <c r="H18" s="200"/>
+      <c r="I18" s="200"/>
+      <c r="J18" s="227"/>
       <c r="K18" s="26"/>
     </row>
-    <row r="19" spans="1:11" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="210"/>
-      <c r="B19" s="161"/>
-      <c r="C19" s="213"/>
+    <row r="19" spans="1:11" ht="33" x14ac:dyDescent="0.25">
+      <c r="A19" s="220"/>
+      <c r="B19" s="171"/>
+      <c r="C19" s="223"/>
       <c r="D19" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E19" s="156"/>
-      <c r="F19" s="156"/>
-      <c r="G19" s="156"/>
-      <c r="H19" s="156"/>
-      <c r="I19" s="156"/>
-      <c r="J19" s="207"/>
+      <c r="E19" s="200"/>
+      <c r="F19" s="200"/>
+      <c r="G19" s="200"/>
+      <c r="H19" s="200"/>
+      <c r="I19" s="200"/>
+      <c r="J19" s="227"/>
       <c r="K19" s="26"/>
     </row>
-    <row r="20" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="210"/>
-      <c r="B20" s="161"/>
-      <c r="C20" s="213"/>
+    <row r="20" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="220"/>
+      <c r="B20" s="171"/>
+      <c r="C20" s="223"/>
       <c r="D20" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E20" s="156"/>
-      <c r="F20" s="156"/>
-      <c r="G20" s="156"/>
-      <c r="H20" s="156"/>
-      <c r="I20" s="156"/>
-      <c r="J20" s="207"/>
+      <c r="E20" s="200"/>
+      <c r="F20" s="200"/>
+      <c r="G20" s="200"/>
+      <c r="H20" s="200"/>
+      <c r="I20" s="200"/>
+      <c r="J20" s="227"/>
       <c r="K20" s="27"/>
     </row>
-    <row r="21" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="210"/>
-      <c r="B21" s="161"/>
-      <c r="C21" s="213"/>
+    <row r="21" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="220"/>
+      <c r="B21" s="171"/>
+      <c r="C21" s="223"/>
       <c r="D21" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E21" s="156"/>
-      <c r="F21" s="156"/>
-      <c r="G21" s="156"/>
-      <c r="H21" s="156"/>
-      <c r="I21" s="156"/>
-      <c r="J21" s="207"/>
+      <c r="E21" s="200"/>
+      <c r="F21" s="200"/>
+      <c r="G21" s="200"/>
+      <c r="H21" s="200"/>
+      <c r="I21" s="200"/>
+      <c r="J21" s="227"/>
       <c r="K21" s="27"/>
     </row>
-    <row r="22" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="211"/>
-      <c r="B22" s="162"/>
-      <c r="C22" s="214"/>
+    <row r="22" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="221"/>
+      <c r="B22" s="172"/>
+      <c r="C22" s="224"/>
       <c r="D22" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E22" s="157"/>
-      <c r="F22" s="157"/>
-      <c r="G22" s="157"/>
-      <c r="H22" s="157"/>
-      <c r="I22" s="157"/>
-      <c r="J22" s="208"/>
+      <c r="E22" s="201"/>
+      <c r="F22" s="201"/>
+      <c r="G22" s="201"/>
+      <c r="H22" s="201"/>
+      <c r="I22" s="201"/>
+      <c r="J22" s="228"/>
       <c r="K22" s="27"/>
     </row>
-    <row r="23" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A23" s="29">
         <f>IF(LEN(C23)=0,"",COUNTA($C$17:C23))</f>
         <v>2</v>
@@ -6959,7 +6968,7 @@
       <c r="J23" s="34"/>
       <c r="K23" s="27"/>
     </row>
-    <row r="24" spans="1:11" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="33" x14ac:dyDescent="0.25">
       <c r="A24" s="29">
         <f>IF(LEN(C24)=0,"",COUNTA($C$17:C24))</f>
         <v>3</v>
@@ -6985,14 +6994,14 @@
       <c r="J24" s="34"/>
       <c r="K24" s="27"/>
     </row>
-    <row r="25" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="127" t="s">
         <v>416</v>
       </c>
-      <c r="B25" s="202" t="s">
+      <c r="B25" s="216" t="s">
         <v>417</v>
       </c>
-      <c r="C25" s="203"/>
+      <c r="C25" s="217"/>
       <c r="D25" s="128"/>
       <c r="E25" s="129"/>
       <c r="F25" s="129"/>
@@ -7002,7 +7011,7 @@
       <c r="J25" s="130"/>
       <c r="K25" s="126"/>
     </row>
-    <row r="26" spans="1:11" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="66" x14ac:dyDescent="0.25">
       <c r="A26" s="29">
         <f>IF(LEN(C26)=0,"",COUNTA($C$17:C26))</f>
         <v>4</v>
@@ -7034,7 +7043,7 @@
       <c r="J26" s="34"/>
       <c r="K26" s="27"/>
     </row>
-    <row r="27" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A27" s="29">
         <f>IF(LEN(C27)=0,"",COUNTA($C$17:C27))</f>
         <v>5</v>
@@ -7066,7 +7075,7 @@
       <c r="J27" s="34"/>
       <c r="K27" s="27"/>
     </row>
-    <row r="28" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="29">
         <f>IF(LEN(C28)=0,"",COUNTA($C$17:C28))</f>
         <v>6</v>
@@ -7098,92 +7107,92 @@
       <c r="J28" s="34"/>
       <c r="K28" s="27"/>
     </row>
-    <row r="29" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A29" s="29">
         <f>IF(LEN(C29)=0,"",COUNTA($C$17:C29))</f>
         <v>7</v>
       </c>
-      <c r="B29" s="160" t="s">
+      <c r="B29" s="170" t="s">
         <v>410</v>
       </c>
       <c r="C29" s="24" t="s">
         <v>387</v>
       </c>
       <c r="D29" s="24"/>
-      <c r="E29" s="155">
+      <c r="E29" s="199">
         <v>183000</v>
       </c>
-      <c r="F29" s="155">
+      <c r="F29" s="199">
         <v>183000</v>
       </c>
-      <c r="G29" s="155">
+      <c r="G29" s="199">
         <v>183000</v>
       </c>
-      <c r="H29" s="215"/>
-      <c r="I29" s="215"/>
-      <c r="J29" s="168"/>
+      <c r="H29" s="204"/>
+      <c r="I29" s="204"/>
+      <c r="J29" s="178"/>
       <c r="K29" s="27"/>
     </row>
-    <row r="30" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A30" s="29">
         <f>IF(LEN(C30)=0,"",COUNTA($C$17:C30))</f>
         <v>8</v>
       </c>
-      <c r="B30" s="161"/>
+      <c r="B30" s="171"/>
       <c r="C30" s="24" t="s">
         <v>388</v>
       </c>
       <c r="D30" s="24"/>
-      <c r="E30" s="156"/>
-      <c r="F30" s="156"/>
-      <c r="G30" s="156"/>
-      <c r="H30" s="216"/>
-      <c r="I30" s="216"/>
-      <c r="J30" s="201"/>
+      <c r="E30" s="200"/>
+      <c r="F30" s="200"/>
+      <c r="G30" s="200"/>
+      <c r="H30" s="205"/>
+      <c r="I30" s="205"/>
+      <c r="J30" s="225"/>
       <c r="K30" s="27"/>
     </row>
-    <row r="31" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A31" s="29">
         <f>IF(LEN(C31)=0,"",COUNTA($C$17:C31))</f>
         <v>9</v>
       </c>
-      <c r="B31" s="161"/>
+      <c r="B31" s="171"/>
       <c r="C31" s="24" t="s">
         <v>389</v>
       </c>
       <c r="D31" s="24"/>
-      <c r="E31" s="156"/>
-      <c r="F31" s="156"/>
-      <c r="G31" s="156"/>
-      <c r="H31" s="216"/>
-      <c r="I31" s="216"/>
-      <c r="J31" s="201"/>
+      <c r="E31" s="200"/>
+      <c r="F31" s="200"/>
+      <c r="G31" s="200"/>
+      <c r="H31" s="205"/>
+      <c r="I31" s="205"/>
+      <c r="J31" s="225"/>
       <c r="K31" s="27"/>
     </row>
-    <row r="32" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A32" s="29">
         <f>IF(LEN(C32)=0,"",COUNTA($C$17:C32))</f>
         <v>10</v>
       </c>
-      <c r="B32" s="162"/>
+      <c r="B32" s="172"/>
       <c r="C32" s="31" t="s">
         <v>390</v>
       </c>
       <c r="D32" s="24"/>
-      <c r="E32" s="157"/>
-      <c r="F32" s="157"/>
-      <c r="G32" s="157"/>
-      <c r="H32" s="217"/>
-      <c r="I32" s="217"/>
-      <c r="J32" s="169"/>
+      <c r="E32" s="201"/>
+      <c r="F32" s="201"/>
+      <c r="G32" s="201"/>
+      <c r="H32" s="206"/>
+      <c r="I32" s="206"/>
+      <c r="J32" s="179"/>
       <c r="K32" s="27"/>
     </row>
-    <row r="33" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="29">
         <f>IF(LEN(C33)=0,"",COUNTA($C$17:C33))</f>
         <v>11</v>
       </c>
-      <c r="B33" s="163" t="s">
+      <c r="B33" s="195" t="s">
         <v>28</v>
       </c>
       <c r="C33" s="35" t="s">
@@ -7192,47 +7201,47 @@
       <c r="D33" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="E33" s="204">
+      <c r="E33" s="207">
         <v>48000</v>
       </c>
-      <c r="F33" s="204">
+      <c r="F33" s="207">
         <v>48000</v>
       </c>
-      <c r="G33" s="204">
+      <c r="G33" s="207">
         <v>48000</v>
       </c>
-      <c r="H33" s="204">
+      <c r="H33" s="207">
         <v>48000</v>
       </c>
-      <c r="I33" s="204">
+      <c r="I33" s="207">
         <v>48000</v>
       </c>
-      <c r="J33" s="179" t="s">
+      <c r="J33" s="148" t="s">
         <v>31</v>
       </c>
       <c r="K33" s="27"/>
     </row>
-    <row r="34" spans="1:11" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" ht="33" x14ac:dyDescent="0.25">
       <c r="A34" s="29">
         <f>IF(LEN(C34)=0,"",COUNTA($C$17:C34))</f>
         <v>12</v>
       </c>
-      <c r="B34" s="163"/>
+      <c r="B34" s="195"/>
       <c r="C34" s="35" t="s">
         <v>32</v>
       </c>
       <c r="D34" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="E34" s="205"/>
-      <c r="F34" s="205"/>
-      <c r="G34" s="205"/>
-      <c r="H34" s="205"/>
-      <c r="I34" s="205"/>
-      <c r="J34" s="180"/>
+      <c r="E34" s="208"/>
+      <c r="F34" s="208"/>
+      <c r="G34" s="208"/>
+      <c r="H34" s="208"/>
+      <c r="I34" s="208"/>
+      <c r="J34" s="149"/>
       <c r="K34" s="27"/>
     </row>
-    <row r="35" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A35" s="29">
         <f>IF(LEN(C35)=0,"",COUNTA($C$17:C35))</f>
         <v>13</v>
@@ -7264,12 +7273,12 @@
       <c r="J35" s="34"/>
       <c r="K35" s="27"/>
     </row>
-    <row r="36" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="29">
         <f>IF(LEN(C36)=0,"",COUNTA($C$17:C36))</f>
         <v>14</v>
       </c>
-      <c r="B36" s="178"/>
+      <c r="B36" s="191"/>
       <c r="C36" s="35" t="s">
         <v>56</v>
       </c>
@@ -7291,15 +7300,15 @@
       <c r="I36" s="67">
         <v>59000</v>
       </c>
-      <c r="J36" s="153"/>
+      <c r="J36" s="174"/>
       <c r="K36" s="27"/>
     </row>
-    <row r="37" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="29">
         <f>IF(LEN(C37)=0,"",COUNTA($C$17:C37))</f>
         <v>15</v>
       </c>
-      <c r="B37" s="178"/>
+      <c r="B37" s="191"/>
       <c r="C37" s="35" t="s">
         <v>60</v>
       </c>
@@ -7321,10 +7330,10 @@
       <c r="I37" s="67">
         <v>41000</v>
       </c>
-      <c r="J37" s="154"/>
+      <c r="J37" s="175"/>
       <c r="K37" s="27"/>
     </row>
-    <row r="38" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A38" s="29">
         <f>IF(LEN(C38)=0,"",COUNTA($C$17:C38))</f>
         <v>16</v>
@@ -7354,7 +7363,7 @@
       <c r="J38" s="34"/>
       <c r="K38" s="27"/>
     </row>
-    <row r="39" spans="1:11" s="52" customFormat="1" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" s="52" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A39" s="29">
         <f>IF(LEN(C39)=0,"",COUNTA($C$17:C39))</f>
         <v>17</v>
@@ -7384,7 +7393,7 @@
       <c r="J39" s="34"/>
       <c r="K39" s="51"/>
     </row>
-    <row r="40" spans="1:11" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" ht="33" x14ac:dyDescent="0.25">
       <c r="A40" s="29">
         <f>IF(LEN(C40)=0,"",COUNTA($C$17:C40))</f>
         <v>18</v>
@@ -7410,14 +7419,14 @@
       <c r="J40" s="34"/>
       <c r="K40" s="27"/>
     </row>
-    <row r="41" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="127" t="s">
         <v>416</v>
       </c>
-      <c r="B41" s="202" t="s">
+      <c r="B41" s="216" t="s">
         <v>418</v>
       </c>
-      <c r="C41" s="203"/>
+      <c r="C41" s="217"/>
       <c r="D41" s="128"/>
       <c r="E41" s="129"/>
       <c r="F41" s="129"/>
@@ -7427,7 +7436,7 @@
       <c r="J41" s="130"/>
       <c r="K41" s="126"/>
     </row>
-    <row r="42" spans="1:11" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" ht="33" x14ac:dyDescent="0.25">
       <c r="A42" s="29">
         <f>IF(LEN(C42)=0,"",COUNTA($C$17:C42))</f>
         <v>19</v>
@@ -7459,7 +7468,7 @@
       <c r="J42" s="34"/>
       <c r="K42" s="27"/>
     </row>
-    <row r="43" spans="1:11" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" ht="33" x14ac:dyDescent="0.25">
       <c r="A43" s="29">
         <f>IF(LEN(C43)=0,"",COUNTA($C$17:C43))</f>
         <v>20</v>
@@ -7483,7 +7492,7 @@
       <c r="J43" s="34"/>
       <c r="K43" s="27"/>
     </row>
-    <row r="44" spans="1:11" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" ht="33" x14ac:dyDescent="0.25">
       <c r="A44" s="29">
         <f>IF(LEN(C44)=0,"",COUNTA($C$17:C44))</f>
         <v>21</v>
@@ -7513,12 +7522,12 @@
       <c r="J44" s="34"/>
       <c r="K44" s="27"/>
     </row>
-    <row r="45" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A45" s="29">
         <f>IF(LEN(C45)=0,"",COUNTA($C$17:C45))</f>
         <v>22</v>
       </c>
-      <c r="B45" s="158" t="s">
+      <c r="B45" s="193" t="s">
         <v>209</v>
       </c>
       <c r="C45" s="31" t="s">
@@ -7545,12 +7554,12 @@
       <c r="J45" s="34"/>
       <c r="K45" s="27"/>
     </row>
-    <row r="46" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A46" s="29">
         <f>IF(LEN(C46)=0,"",COUNTA($C$17:C46))</f>
         <v>23</v>
       </c>
-      <c r="B46" s="159"/>
+      <c r="B46" s="194"/>
       <c r="C46" s="31" t="s">
         <v>212</v>
       </c>
@@ -7571,12 +7580,12 @@
       <c r="J46" s="34"/>
       <c r="K46" s="27"/>
     </row>
-    <row r="47" spans="1:11" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" ht="33" x14ac:dyDescent="0.25">
       <c r="A47" s="29">
         <f>IF(LEN(C47)=0,"",COUNTA($C$17:C47))</f>
         <v>24</v>
       </c>
-      <c r="B47" s="220"/>
+      <c r="B47" s="215"/>
       <c r="C47" s="31" t="s">
         <v>214</v>
       </c>
@@ -7601,7 +7610,7 @@
       <c r="J47" s="34"/>
       <c r="K47" s="27"/>
     </row>
-    <row r="48" spans="1:11" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" ht="33" x14ac:dyDescent="0.25">
       <c r="A48" s="29">
         <f>IF(LEN(C48)=0,"",COUNTA($C$17:C48))</f>
         <v>25</v>
@@ -7629,7 +7638,7 @@
       <c r="J48" s="34"/>
       <c r="K48" s="27"/>
     </row>
-    <row r="49" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A49" s="29">
         <f>IF(LEN(C49)=0,"",COUNTA($C$17:C49))</f>
         <v>26</v>
@@ -7659,13 +7668,13 @@
       <c r="J49" s="34"/>
       <c r="K49" s="27"/>
     </row>
-    <row r="50" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="199" t="s">
+    <row r="50" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A50" s="168" t="s">
         <v>38</v>
       </c>
-      <c r="B50" s="219"/>
-      <c r="C50" s="219"/>
-      <c r="D50" s="200"/>
+      <c r="B50" s="214"/>
+      <c r="C50" s="214"/>
+      <c r="D50" s="169"/>
       <c r="E50" s="21"/>
       <c r="F50" s="21">
         <f>SUM(F17:F49)</f>
@@ -7686,7 +7695,7 @@
       <c r="J50" s="41"/>
       <c r="K50" s="27"/>
     </row>
-    <row r="51" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A51" s="42"/>
       <c r="B51" s="43"/>
       <c r="C51" s="44"/>
@@ -7699,13 +7708,13 @@
       <c r="J51" s="46"/>
       <c r="K51" s="27"/>
     </row>
-    <row r="52" spans="1:11" s="110" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="146" t="s">
+    <row r="52" spans="1:11" s="110" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A52" s="196" t="s">
         <v>396</v>
       </c>
-      <c r="B52" s="146"/>
-      <c r="C52" s="146"/>
-      <c r="D52" s="146"/>
+      <c r="B52" s="196"/>
+      <c r="C52" s="196"/>
+      <c r="D52" s="196"/>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
       <c r="G52" s="7"/>
@@ -7713,77 +7722,77 @@
       <c r="I52" s="7"/>
       <c r="J52" s="109"/>
     </row>
-    <row r="53" spans="1:11" s="110" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" s="110" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A53" s="111"/>
-      <c r="B53" s="143" t="s">
+      <c r="B53" s="202" t="s">
         <v>397</v>
       </c>
-      <c r="C53" s="143"/>
-      <c r="D53" s="143"/>
-      <c r="E53" s="143"/>
-      <c r="F53" s="143"/>
-      <c r="G53" s="143"/>
-      <c r="H53" s="143"/>
-      <c r="I53" s="143"/>
-      <c r="J53" s="143"/>
-    </row>
-    <row r="54" spans="1:11" s="110" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="C53" s="202"/>
+      <c r="D53" s="202"/>
+      <c r="E53" s="202"/>
+      <c r="F53" s="202"/>
+      <c r="G53" s="202"/>
+      <c r="H53" s="202"/>
+      <c r="I53" s="202"/>
+      <c r="J53" s="202"/>
+    </row>
+    <row r="54" spans="1:11" s="110" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A54" s="111"/>
-      <c r="B54" s="143" t="s">
+      <c r="B54" s="202" t="s">
         <v>398</v>
       </c>
-      <c r="C54" s="143"/>
-      <c r="D54" s="143"/>
-      <c r="E54" s="143"/>
-      <c r="F54" s="143"/>
-      <c r="G54" s="143"/>
-      <c r="H54" s="143"/>
-      <c r="I54" s="143"/>
-      <c r="J54" s="143"/>
-    </row>
-    <row r="55" spans="1:11" s="113" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C54" s="202"/>
+      <c r="D54" s="202"/>
+      <c r="E54" s="202"/>
+      <c r="F54" s="202"/>
+      <c r="G54" s="202"/>
+      <c r="H54" s="202"/>
+      <c r="I54" s="202"/>
+      <c r="J54" s="202"/>
+    </row>
+    <row r="55" spans="1:11" s="113" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="112"/>
-      <c r="B55" s="143" t="s">
+      <c r="B55" s="202" t="s">
         <v>399</v>
       </c>
-      <c r="C55" s="143"/>
-      <c r="D55" s="143"/>
-      <c r="E55" s="143"/>
-      <c r="F55" s="143"/>
-      <c r="G55" s="143"/>
-      <c r="H55" s="143"/>
-      <c r="I55" s="143"/>
-      <c r="J55" s="143"/>
-    </row>
-    <row r="56" spans="1:11" s="115" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C55" s="202"/>
+      <c r="D55" s="202"/>
+      <c r="E55" s="202"/>
+      <c r="F55" s="202"/>
+      <c r="G55" s="202"/>
+      <c r="H55" s="202"/>
+      <c r="I55" s="202"/>
+      <c r="J55" s="202"/>
+    </row>
+    <row r="56" spans="1:11" s="115" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="114"/>
-      <c r="B56" s="144" t="s">
+      <c r="B56" s="203" t="s">
         <v>400</v>
       </c>
-      <c r="C56" s="144"/>
-      <c r="D56" s="144"/>
-      <c r="E56" s="144"/>
-      <c r="F56" s="144"/>
-      <c r="G56" s="144"/>
-      <c r="H56" s="144"/>
-      <c r="I56" s="144"/>
-      <c r="J56" s="144"/>
-    </row>
-    <row r="57" spans="1:11" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C56" s="203"/>
+      <c r="D56" s="203"/>
+      <c r="E56" s="203"/>
+      <c r="F56" s="203"/>
+      <c r="G56" s="203"/>
+      <c r="H56" s="203"/>
+      <c r="I56" s="203"/>
+      <c r="J56" s="203"/>
+    </row>
+    <row r="57" spans="1:11" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="109"/>
-      <c r="B57" s="143" t="s">
+      <c r="B57" s="202" t="s">
         <v>401</v>
       </c>
-      <c r="C57" s="143"/>
-      <c r="D57" s="143"/>
-      <c r="E57" s="143"/>
-      <c r="F57" s="143"/>
-      <c r="G57" s="143"/>
-      <c r="H57" s="143"/>
-      <c r="I57" s="143"/>
-      <c r="J57" s="143"/>
-    </row>
-    <row r="58" spans="1:11" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="C57" s="202"/>
+      <c r="D57" s="202"/>
+      <c r="E57" s="202"/>
+      <c r="F57" s="202"/>
+      <c r="G57" s="202"/>
+      <c r="H57" s="202"/>
+      <c r="I57" s="202"/>
+      <c r="J57" s="202"/>
+    </row>
+    <row r="58" spans="1:11" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A58" s="109"/>
       <c r="B58" s="112" t="s">
         <v>402</v>
@@ -7797,7 +7806,7 @@
       <c r="I58" s="7"/>
       <c r="J58" s="5"/>
     </row>
-    <row r="59" spans="1:11" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A59" s="109"/>
       <c r="B59" s="112" t="s">
         <v>403</v>
@@ -7811,7 +7820,7 @@
       <c r="I59" s="7"/>
       <c r="J59" s="5"/>
     </row>
-    <row r="60" spans="1:11" s="121" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" s="121" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A60" s="117" t="s">
         <v>404</v>
       </c>
@@ -7825,7 +7834,7 @@
       <c r="I60" s="119"/>
       <c r="J60" s="120"/>
     </row>
-    <row r="61" spans="1:11" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A61" s="109"/>
       <c r="B61" s="5" t="s">
         <v>405</v>
@@ -7841,7 +7850,7 @@
       <c r="I61" s="10"/>
       <c r="J61" s="5"/>
     </row>
-    <row r="62" spans="1:11" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A62" s="109"/>
       <c r="B62" s="5" t="s">
         <v>407</v>
@@ -7855,7 +7864,7 @@
       <c r="I62" s="10"/>
       <c r="J62" s="5"/>
     </row>
-    <row r="63" spans="1:11" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A63" s="109"/>
       <c r="B63" s="5" t="s">
         <v>408</v>
@@ -7871,34 +7880,6 @@
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="I29:I32"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="E17:E22"/>
-    <mergeCell ref="E29:E32"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="B55:J55"/>
-    <mergeCell ref="B56:J56"/>
-    <mergeCell ref="B57:J57"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="B53:J53"/>
-    <mergeCell ref="B54:J54"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="D1:J5"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="B9:J9"/>
-    <mergeCell ref="A10:J11"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="A17:A22"/>
-    <mergeCell ref="B17:B22"/>
-    <mergeCell ref="C17:C22"/>
-    <mergeCell ref="H29:H32"/>
-    <mergeCell ref="H33:H34"/>
     <mergeCell ref="J29:J32"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B16:C16"/>
@@ -7915,6 +7896,34 @@
     <mergeCell ref="G33:G34"/>
     <mergeCell ref="B33:B34"/>
     <mergeCell ref="I17:I22"/>
+    <mergeCell ref="A17:A22"/>
+    <mergeCell ref="B17:B22"/>
+    <mergeCell ref="C17:C22"/>
+    <mergeCell ref="H29:H32"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="D1:J5"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="B9:J9"/>
+    <mergeCell ref="A10:J11"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B55:J55"/>
+    <mergeCell ref="B56:J56"/>
+    <mergeCell ref="B57:J57"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="B53:J53"/>
+    <mergeCell ref="B54:J54"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="I29:I32"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="E17:E22"/>
+    <mergeCell ref="E29:E32"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="E13:E14"/>
   </mergeCells>
   <pageMargins left="0.35433070866141736" right="0.15748031496062992" top="0.23622047244094491" bottom="0.19685039370078741" header="0.15748031496062992" footer="0.15748031496062992"/>
   <pageSetup paperSize="9" scale="41" fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -7931,62 +7940,62 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K48"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="19" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" style="122" customWidth="1"/>
-    <col min="3" max="3" width="53.33203125" style="19" customWidth="1"/>
-    <col min="4" max="4" width="48.5546875" style="19" customWidth="1"/>
-    <col min="5" max="5" width="16.44140625" style="123" customWidth="1"/>
-    <col min="6" max="6" width="28.33203125" style="124" customWidth="1"/>
-    <col min="7" max="7" width="19.6640625" style="19" customWidth="1"/>
-    <col min="8" max="8" width="9.88671875" style="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.109375" style="19"/>
+    <col min="2" max="2" width="13.42578125" style="122" customWidth="1"/>
+    <col min="3" max="3" width="53.28515625" style="19" customWidth="1"/>
+    <col min="4" max="4" width="48.5703125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" style="123" customWidth="1"/>
+    <col min="6" max="6" width="28.28515625" style="124" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" style="19" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="181" t="s">
+      <c r="D1" s="150" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="182"/>
-      <c r="F1" s="183"/>
-    </row>
-    <row r="2" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E1" s="151"/>
+      <c r="F1" s="152"/>
+    </row>
+    <row r="2" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="181"/>
-      <c r="E2" s="182"/>
-      <c r="F2" s="183"/>
-    </row>
-    <row r="3" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D2" s="150"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="152"/>
+    </row>
+    <row r="3" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="181"/>
-      <c r="E3" s="182"/>
-      <c r="F3" s="183"/>
-    </row>
-    <row r="4" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D3" s="150"/>
+      <c r="E3" s="151"/>
+      <c r="F3" s="152"/>
+    </row>
+    <row r="4" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="181"/>
-      <c r="E4" s="182"/>
-      <c r="F4" s="183"/>
-    </row>
-    <row r="5" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D4" s="150"/>
+      <c r="E4" s="151"/>
+      <c r="F4" s="152"/>
+    </row>
+    <row r="5" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="184"/>
-      <c r="E5" s="185"/>
-      <c r="F5" s="186"/>
-    </row>
-    <row r="6" spans="1:11" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="D5" s="153"/>
+      <c r="E5" s="154"/>
+      <c r="F5" s="155"/>
+    </row>
+    <row r="6" spans="1:11" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -7994,22 +8003,22 @@
       <c r="E6" s="7"/>
       <c r="F6" s="5"/>
     </row>
-    <row r="7" spans="1:11" s="4" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A7" s="187" t="s">
+    <row r="7" spans="1:11" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="156" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="188"/>
-      <c r="C7" s="188"/>
-      <c r="D7" s="188"/>
-      <c r="E7" s="188"/>
-      <c r="F7" s="189"/>
+      <c r="B7" s="157"/>
+      <c r="C7" s="157"/>
+      <c r="D7" s="157"/>
+      <c r="E7" s="157"/>
+      <c r="F7" s="158"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
     </row>
-    <row r="8" spans="1:11" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -8022,49 +8031,49 @@
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
     </row>
-    <row r="9" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
-      <c r="B9" s="190" t="s">
+      <c r="B9" s="159" t="s">
         <v>409</v>
       </c>
-      <c r="C9" s="191"/>
-      <c r="D9" s="191"/>
-      <c r="E9" s="191"/>
-      <c r="F9" s="192"/>
+      <c r="C9" s="160"/>
+      <c r="D9" s="160"/>
+      <c r="E9" s="160"/>
+      <c r="F9" s="161"/>
       <c r="G9" s="12"/>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
     </row>
-    <row r="10" spans="1:11" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="193" t="s">
+    <row r="10" spans="1:11" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="162" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="194"/>
-      <c r="C10" s="194"/>
-      <c r="D10" s="194"/>
-      <c r="E10" s="194"/>
-      <c r="F10" s="195"/>
+      <c r="B10" s="163"/>
+      <c r="C10" s="163"/>
+      <c r="D10" s="163"/>
+      <c r="E10" s="163"/>
+      <c r="F10" s="164"/>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
     </row>
-    <row r="11" spans="1:11" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="196"/>
-      <c r="B11" s="197"/>
-      <c r="C11" s="197"/>
-      <c r="D11" s="197"/>
-      <c r="E11" s="197"/>
-      <c r="F11" s="198"/>
+    <row r="11" spans="1:11" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="165"/>
+      <c r="B11" s="166"/>
+      <c r="C11" s="166"/>
+      <c r="D11" s="166"/>
+      <c r="E11" s="166"/>
+      <c r="F11" s="167"/>
       <c r="G11" s="14"/>
       <c r="H11" s="14"/>
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
       <c r="K11" s="14"/>
     </row>
-    <row r="12" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="15"/>
@@ -8072,7 +8081,7 @@
       <c r="E12" s="17"/>
       <c r="F12" s="134"/>
     </row>
-    <row r="13" spans="1:11" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="33" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>3</v>
       </c>
@@ -8091,100 +8100,100 @@
       </c>
       <c r="G13" s="23"/>
     </row>
-    <row r="14" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="127" t="s">
         <v>411</v>
       </c>
-      <c r="B14" s="202" t="s">
+      <c r="B14" s="216" t="s">
         <v>420</v>
       </c>
-      <c r="C14" s="203"/>
+      <c r="C14" s="217"/>
       <c r="D14" s="128"/>
       <c r="E14" s="129"/>
       <c r="F14" s="130"/>
       <c r="G14" s="126"/>
     </row>
-    <row r="15" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="209">
+    <row r="15" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="219">
         <f>IF(LEN(C15)=0,"",COUNTA($C$15:C15))</f>
         <v>1</v>
       </c>
-      <c r="B15" s="160" t="s">
+      <c r="B15" s="170" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="212" t="s">
+      <c r="C15" s="222" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="155">
+      <c r="E15" s="199">
         <v>120000</v>
       </c>
-      <c r="F15" s="206"/>
+      <c r="F15" s="226"/>
       <c r="G15" s="26"/>
     </row>
-    <row r="16" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="210"/>
-      <c r="B16" s="161"/>
-      <c r="C16" s="213"/>
+    <row r="16" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="220"/>
+      <c r="B16" s="171"/>
+      <c r="C16" s="223"/>
       <c r="D16" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="156"/>
-      <c r="F16" s="207"/>
+      <c r="E16" s="200"/>
+      <c r="F16" s="227"/>
       <c r="G16" s="26"/>
     </row>
-    <row r="17" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="210"/>
-      <c r="B17" s="161"/>
-      <c r="C17" s="213"/>
+    <row r="17" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A17" s="220"/>
+      <c r="B17" s="171"/>
+      <c r="C17" s="223"/>
       <c r="D17" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="156"/>
-      <c r="F17" s="207"/>
+      <c r="E17" s="200"/>
+      <c r="F17" s="227"/>
       <c r="G17" s="26"/>
     </row>
-    <row r="18" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="210"/>
-      <c r="B18" s="161"/>
-      <c r="C18" s="213"/>
+    <row r="18" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="220"/>
+      <c r="B18" s="171"/>
+      <c r="C18" s="223"/>
       <c r="D18" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E18" s="156"/>
-      <c r="F18" s="207"/>
+      <c r="E18" s="200"/>
+      <c r="F18" s="227"/>
       <c r="G18" s="27"/>
     </row>
-    <row r="19" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="210"/>
-      <c r="B19" s="161"/>
-      <c r="C19" s="213"/>
+    <row r="19" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="220"/>
+      <c r="B19" s="171"/>
+      <c r="C19" s="223"/>
       <c r="D19" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="156"/>
-      <c r="F19" s="207"/>
+      <c r="E19" s="200"/>
+      <c r="F19" s="227"/>
       <c r="G19" s="27"/>
     </row>
-    <row r="20" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="211"/>
-      <c r="B20" s="162"/>
-      <c r="C20" s="214"/>
+    <row r="20" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="221"/>
+      <c r="B20" s="172"/>
+      <c r="C20" s="224"/>
       <c r="D20" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="157"/>
-      <c r="F20" s="208"/>
+      <c r="E20" s="201"/>
+      <c r="F20" s="228"/>
       <c r="G20" s="27"/>
     </row>
-    <row r="21" spans="1:7" s="95" customFormat="1" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" s="95" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A21" s="29">
         <f>IF(LEN(C21)=0,"",COUNTA($C$15:C21))</f>
         <v>2</v>
       </c>
-      <c r="B21" s="160" t="s">
+      <c r="B21" s="170" t="s">
         <v>316</v>
       </c>
       <c r="C21" s="24" t="s">
@@ -8198,12 +8207,12 @@
       </c>
       <c r="F21" s="34"/>
     </row>
-    <row r="22" spans="1:7" s="95" customFormat="1" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" s="95" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A22" s="29">
         <f>IF(LEN(C22)=0,"",COUNTA($C$15:C22))</f>
         <v>3</v>
       </c>
-      <c r="B22" s="161"/>
+      <c r="B22" s="171"/>
       <c r="C22" s="24" t="s">
         <v>319</v>
       </c>
@@ -8215,12 +8224,12 @@
       </c>
       <c r="F22" s="34"/>
     </row>
-    <row r="23" spans="1:7" s="95" customFormat="1" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" s="95" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A23" s="29">
         <f>IF(LEN(C23)=0,"",COUNTA($C$15:C23))</f>
         <v>4</v>
       </c>
-      <c r="B23" s="162"/>
+      <c r="B23" s="172"/>
       <c r="C23" s="24" t="s">
         <v>421</v>
       </c>
@@ -8230,7 +8239,7 @@
       </c>
       <c r="F23" s="34"/>
     </row>
-    <row r="24" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A24" s="29">
         <f>IF(LEN(C24)=0,"",COUNTA($C$15:C24))</f>
         <v>5</v>
@@ -8250,7 +8259,7 @@
       <c r="F24" s="34"/>
       <c r="G24" s="27"/>
     </row>
-    <row r="25" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A25" s="29">
         <f>IF(LEN(C25)=0,"",COUNTA($C$15:C25))</f>
         <v>6</v>
@@ -8270,7 +8279,7 @@
       <c r="F25" s="34"/>
       <c r="G25" s="27"/>
     </row>
-    <row r="26" spans="1:7" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="29">
         <f>IF(LEN(C26)=0,"",COUNTA($C$15:C26))</f>
         <v>7</v>
@@ -8290,12 +8299,12 @@
       <c r="F26" s="34"/>
       <c r="G26" s="27"/>
     </row>
-    <row r="27" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="29">
         <f>IF(LEN(C27)=0,"",COUNTA($C$15:C27))</f>
         <v>8</v>
       </c>
-      <c r="B27" s="163" t="s">
+      <c r="B27" s="195" t="s">
         <v>28</v>
       </c>
       <c r="C27" s="35" t="s">
@@ -8304,31 +8313,31 @@
       <c r="D27" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="E27" s="204">
+      <c r="E27" s="207">
         <v>48000</v>
       </c>
-      <c r="F27" s="152" t="s">
+      <c r="F27" s="173" t="s">
         <v>31</v>
       </c>
       <c r="G27" s="27"/>
     </row>
-    <row r="28" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A28" s="29">
         <f>IF(LEN(C28)=0,"",COUNTA($C$15:C28))</f>
         <v>9</v>
       </c>
-      <c r="B28" s="163"/>
+      <c r="B28" s="195"/>
       <c r="C28" s="35" t="s">
         <v>32</v>
       </c>
       <c r="D28" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="E28" s="205"/>
-      <c r="F28" s="154"/>
+      <c r="E28" s="208"/>
+      <c r="F28" s="175"/>
       <c r="G28" s="27"/>
     </row>
-    <row r="29" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A29" s="29">
         <f>IF(LEN(C29)=0,"",COUNTA($C$15:C29))</f>
         <v>10</v>
@@ -8348,12 +8357,12 @@
       <c r="F29" s="34"/>
       <c r="G29" s="27"/>
     </row>
-    <row r="30" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="29">
         <f>IF(LEN(C30)=0,"",COUNTA($C$15:C30))</f>
         <v>11</v>
       </c>
-      <c r="B30" s="178"/>
+      <c r="B30" s="191"/>
       <c r="C30" s="35" t="s">
         <v>56</v>
       </c>
@@ -8363,15 +8372,15 @@
       <c r="E30" s="67">
         <v>59000</v>
       </c>
-      <c r="F30" s="153"/>
+      <c r="F30" s="174"/>
       <c r="G30" s="27"/>
     </row>
-    <row r="31" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="29">
         <f>IF(LEN(C31)=0,"",COUNTA($C$15:C31))</f>
         <v>12</v>
       </c>
-      <c r="B31" s="178"/>
+      <c r="B31" s="191"/>
       <c r="C31" s="35" t="s">
         <v>60</v>
       </c>
@@ -8381,10 +8390,10 @@
       <c r="E31" s="67">
         <v>41000</v>
       </c>
-      <c r="F31" s="154"/>
+      <c r="F31" s="175"/>
       <c r="G31" s="27"/>
     </row>
-    <row r="32" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A32" s="29">
         <f>IF(LEN(C32)=0,"",COUNTA($C$15:C32))</f>
         <v>13</v>
@@ -8404,7 +8413,7 @@
       <c r="F32" s="34"/>
       <c r="G32" s="27"/>
     </row>
-    <row r="33" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A33" s="29">
         <f>IF(LEN(C33)=0,"",COUNTA($C$15:C33))</f>
         <v>14</v>
@@ -8420,7 +8429,7 @@
       <c r="F33" s="34"/>
       <c r="G33" s="27"/>
     </row>
-    <row r="34" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A34" s="29">
         <f>IF(LEN(C34)=0,"",COUNTA($C$15:C34))</f>
         <v>15</v>
@@ -8436,13 +8445,13 @@
       <c r="F34" s="34"/>
       <c r="G34" s="27"/>
     </row>
-    <row r="35" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="199" t="s">
+    <row r="35" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="168" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="219"/>
-      <c r="C35" s="219"/>
-      <c r="D35" s="200"/>
+      <c r="B35" s="214"/>
+      <c r="C35" s="214"/>
+      <c r="D35" s="169"/>
       <c r="E35" s="21">
         <f>SUM(E15:E34)</f>
         <v>906000</v>
@@ -8450,7 +8459,7 @@
       <c r="F35" s="41"/>
       <c r="G35" s="27"/>
     </row>
-    <row r="36" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A36" s="42"/>
       <c r="B36" s="43"/>
       <c r="C36" s="44"/>
@@ -8459,67 +8468,67 @@
       <c r="F36" s="46"/>
       <c r="G36" s="27"/>
     </row>
-    <row r="37" spans="1:7" s="110" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="146" t="s">
+    <row r="37" spans="1:7" s="110" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A37" s="196" t="s">
         <v>396</v>
       </c>
-      <c r="B37" s="146"/>
-      <c r="C37" s="146"/>
-      <c r="D37" s="146"/>
+      <c r="B37" s="196"/>
+      <c r="C37" s="196"/>
+      <c r="D37" s="196"/>
       <c r="E37" s="7"/>
       <c r="F37" s="109"/>
     </row>
-    <row r="38" spans="1:7" s="110" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" s="110" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A38" s="111"/>
-      <c r="B38" s="143" t="s">
+      <c r="B38" s="202" t="s">
         <v>397</v>
       </c>
-      <c r="C38" s="143"/>
-      <c r="D38" s="143"/>
-      <c r="E38" s="143"/>
-      <c r="F38" s="143"/>
-    </row>
-    <row r="39" spans="1:7" s="110" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="C38" s="202"/>
+      <c r="D38" s="202"/>
+      <c r="E38" s="202"/>
+      <c r="F38" s="202"/>
+    </row>
+    <row r="39" spans="1:7" s="110" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A39" s="111"/>
-      <c r="B39" s="143" t="s">
+      <c r="B39" s="202" t="s">
         <v>398</v>
       </c>
-      <c r="C39" s="143"/>
-      <c r="D39" s="143"/>
-      <c r="E39" s="143"/>
-      <c r="F39" s="143"/>
-    </row>
-    <row r="40" spans="1:7" s="113" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C39" s="202"/>
+      <c r="D39" s="202"/>
+      <c r="E39" s="202"/>
+      <c r="F39" s="202"/>
+    </row>
+    <row r="40" spans="1:7" s="113" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="112"/>
-      <c r="B40" s="143" t="s">
+      <c r="B40" s="202" t="s">
         <v>399</v>
       </c>
-      <c r="C40" s="143"/>
-      <c r="D40" s="143"/>
-      <c r="E40" s="143"/>
-      <c r="F40" s="143"/>
-    </row>
-    <row r="41" spans="1:7" s="115" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="202"/>
+      <c r="D40" s="202"/>
+      <c r="E40" s="202"/>
+      <c r="F40" s="202"/>
+    </row>
+    <row r="41" spans="1:7" s="115" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="114"/>
-      <c r="B41" s="144" t="s">
+      <c r="B41" s="203" t="s">
         <v>400</v>
       </c>
-      <c r="C41" s="144"/>
-      <c r="D41" s="144"/>
-      <c r="E41" s="144"/>
-      <c r="F41" s="144"/>
-    </row>
-    <row r="42" spans="1:7" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="203"/>
+      <c r="D41" s="203"/>
+      <c r="E41" s="203"/>
+      <c r="F41" s="203"/>
+    </row>
+    <row r="42" spans="1:7" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="109"/>
-      <c r="B42" s="143" t="s">
+      <c r="B42" s="202" t="s">
         <v>401</v>
       </c>
-      <c r="C42" s="143"/>
-      <c r="D42" s="143"/>
-      <c r="E42" s="143"/>
-      <c r="F42" s="143"/>
-    </row>
-    <row r="43" spans="1:7" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="C42" s="202"/>
+      <c r="D42" s="202"/>
+      <c r="E42" s="202"/>
+      <c r="F42" s="202"/>
+    </row>
+    <row r="43" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A43" s="109"/>
       <c r="B43" s="112" t="s">
         <v>402</v>
@@ -8529,7 +8538,7 @@
       <c r="E43" s="7"/>
       <c r="F43" s="5"/>
     </row>
-    <row r="44" spans="1:7" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A44" s="109"/>
       <c r="B44" s="112" t="s">
         <v>403</v>
@@ -8539,7 +8548,7 @@
       <c r="E44" s="7"/>
       <c r="F44" s="5"/>
     </row>
-    <row r="45" spans="1:7" s="121" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" s="121" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A45" s="117" t="s">
         <v>404</v>
       </c>
@@ -8549,7 +8558,7 @@
       <c r="E45" s="119"/>
       <c r="F45" s="120"/>
     </row>
-    <row r="46" spans="1:7" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A46" s="109"/>
       <c r="B46" s="5" t="s">
         <v>405</v>
@@ -8561,7 +8570,7 @@
       <c r="E46" s="10"/>
       <c r="F46" s="5"/>
     </row>
-    <row r="47" spans="1:7" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A47" s="109"/>
       <c r="B47" s="5" t="s">
         <v>407</v>
@@ -8571,7 +8580,7 @@
       <c r="E47" s="10"/>
       <c r="F47" s="5"/>
     </row>
-    <row r="48" spans="1:7" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A48" s="109"/>
       <c r="B48" s="5" t="s">
         <v>408</v>
@@ -8583,17 +8592,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="F15:F20"/>
-    <mergeCell ref="D1:F5"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="A10:F11"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="A15:A20"/>
-    <mergeCell ref="B15:B20"/>
-    <mergeCell ref="C15:C20"/>
-    <mergeCell ref="E15:E20"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="B21:B23"/>
@@ -8607,6 +8605,17 @@
     <mergeCell ref="F27:F28"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="F30:F31"/>
+    <mergeCell ref="F15:F20"/>
+    <mergeCell ref="D1:F5"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="A10:F11"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="A15:A20"/>
+    <mergeCell ref="B15:B20"/>
+    <mergeCell ref="C15:C20"/>
+    <mergeCell ref="E15:E20"/>
   </mergeCells>
   <pageMargins left="0.35433070866141736" right="0.15748031496062992" top="0.23622047244094491" bottom="0.19685039370078741" header="0.15748031496062992" footer="0.15748031496062992"/>
   <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -8620,83 +8629,83 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C5F4D39-A20F-4474-8942-A288520138B9}">
   <dimension ref="A1:O63"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="19" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" style="122" customWidth="1"/>
-    <col min="3" max="3" width="53.33203125" style="19" customWidth="1"/>
-    <col min="4" max="4" width="48.5546875" style="19" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="122" customWidth="1"/>
+    <col min="3" max="3" width="53.28515625" style="19" customWidth="1"/>
+    <col min="4" max="4" width="48.5703125" style="19" customWidth="1"/>
     <col min="5" max="5" width="13" style="123" customWidth="1"/>
-    <col min="6" max="9" width="17.88671875" style="123" customWidth="1"/>
-    <col min="10" max="10" width="28.33203125" style="124" customWidth="1"/>
-    <col min="11" max="11" width="19.6640625" style="19" customWidth="1"/>
-    <col min="12" max="12" width="9.88671875" style="19" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.109375" style="19"/>
+    <col min="6" max="9" width="17.85546875" style="123" customWidth="1"/>
+    <col min="10" max="10" width="28.28515625" style="124" customWidth="1"/>
+    <col min="11" max="11" width="19.7109375" style="19" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" style="19" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="181" t="s">
+      <c r="D1" s="150" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="182"/>
-      <c r="F1" s="182"/>
-      <c r="G1" s="182"/>
-      <c r="H1" s="182"/>
-      <c r="I1" s="182"/>
-      <c r="J1" s="183"/>
-    </row>
-    <row r="2" spans="1:15" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E1" s="151"/>
+      <c r="F1" s="151"/>
+      <c r="G1" s="151"/>
+      <c r="H1" s="151"/>
+      <c r="I1" s="151"/>
+      <c r="J1" s="152"/>
+    </row>
+    <row r="2" spans="1:15" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="181"/>
-      <c r="E2" s="182"/>
-      <c r="F2" s="182"/>
-      <c r="G2" s="182"/>
-      <c r="H2" s="182"/>
-      <c r="I2" s="182"/>
-      <c r="J2" s="183"/>
-    </row>
-    <row r="3" spans="1:15" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D2" s="150"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="151"/>
+      <c r="G2" s="151"/>
+      <c r="H2" s="151"/>
+      <c r="I2" s="151"/>
+      <c r="J2" s="152"/>
+    </row>
+    <row r="3" spans="1:15" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="181"/>
-      <c r="E3" s="182"/>
-      <c r="F3" s="182"/>
-      <c r="G3" s="182"/>
-      <c r="H3" s="182"/>
-      <c r="I3" s="182"/>
-      <c r="J3" s="183"/>
-    </row>
-    <row r="4" spans="1:15" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D3" s="150"/>
+      <c r="E3" s="151"/>
+      <c r="F3" s="151"/>
+      <c r="G3" s="151"/>
+      <c r="H3" s="151"/>
+      <c r="I3" s="151"/>
+      <c r="J3" s="152"/>
+    </row>
+    <row r="4" spans="1:15" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="181"/>
-      <c r="E4" s="182"/>
-      <c r="F4" s="182"/>
-      <c r="G4" s="182"/>
-      <c r="H4" s="182"/>
-      <c r="I4" s="182"/>
-      <c r="J4" s="183"/>
-    </row>
-    <row r="5" spans="1:15" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D4" s="150"/>
+      <c r="E4" s="151"/>
+      <c r="F4" s="151"/>
+      <c r="G4" s="151"/>
+      <c r="H4" s="151"/>
+      <c r="I4" s="151"/>
+      <c r="J4" s="152"/>
+    </row>
+    <row r="5" spans="1:15" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="184"/>
-      <c r="E5" s="185"/>
-      <c r="F5" s="185"/>
-      <c r="G5" s="185"/>
-      <c r="H5" s="185"/>
-      <c r="I5" s="185"/>
-      <c r="J5" s="186"/>
-    </row>
-    <row r="6" spans="1:15" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="D5" s="153"/>
+      <c r="E5" s="154"/>
+      <c r="F5" s="154"/>
+      <c r="G5" s="154"/>
+      <c r="H5" s="154"/>
+      <c r="I5" s="154"/>
+      <c r="J5" s="155"/>
+    </row>
+    <row r="6" spans="1:15" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -8708,26 +8717,26 @@
       <c r="I6" s="7"/>
       <c r="J6" s="5"/>
     </row>
-    <row r="7" spans="1:15" s="4" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A7" s="187" t="s">
+    <row r="7" spans="1:15" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="156" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="188"/>
-      <c r="C7" s="188"/>
-      <c r="D7" s="188"/>
-      <c r="E7" s="188"/>
-      <c r="F7" s="188"/>
-      <c r="G7" s="188"/>
-      <c r="H7" s="188"/>
-      <c r="I7" s="188"/>
-      <c r="J7" s="189"/>
+      <c r="B7" s="157"/>
+      <c r="C7" s="157"/>
+      <c r="D7" s="157"/>
+      <c r="E7" s="157"/>
+      <c r="F7" s="157"/>
+      <c r="G7" s="157"/>
+      <c r="H7" s="157"/>
+      <c r="I7" s="157"/>
+      <c r="J7" s="158"/>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
     </row>
-    <row r="8" spans="1:15" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -8744,61 +8753,61 @@
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
     </row>
-    <row r="9" spans="1:15" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
-      <c r="B9" s="190" t="s">
+      <c r="B9" s="159" t="s">
         <v>409</v>
       </c>
-      <c r="C9" s="191"/>
-      <c r="D9" s="191"/>
-      <c r="E9" s="191"/>
-      <c r="F9" s="191"/>
-      <c r="G9" s="191"/>
-      <c r="H9" s="191"/>
-      <c r="I9" s="191"/>
-      <c r="J9" s="192"/>
+      <c r="C9" s="160"/>
+      <c r="D9" s="160"/>
+      <c r="E9" s="160"/>
+      <c r="F9" s="160"/>
+      <c r="G9" s="160"/>
+      <c r="H9" s="160"/>
+      <c r="I9" s="160"/>
+      <c r="J9" s="161"/>
       <c r="K9" s="12"/>
       <c r="L9" s="12"/>
       <c r="M9" s="12"/>
       <c r="N9" s="12"/>
     </row>
-    <row r="10" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="193" t="s">
+    <row r="10" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="162" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="194"/>
-      <c r="C10" s="194"/>
-      <c r="D10" s="194"/>
-      <c r="E10" s="194"/>
-      <c r="F10" s="194"/>
-      <c r="G10" s="194"/>
-      <c r="H10" s="194"/>
-      <c r="I10" s="194"/>
-      <c r="J10" s="195"/>
+      <c r="B10" s="163"/>
+      <c r="C10" s="163"/>
+      <c r="D10" s="163"/>
+      <c r="E10" s="163"/>
+      <c r="F10" s="163"/>
+      <c r="G10" s="163"/>
+      <c r="H10" s="163"/>
+      <c r="I10" s="163"/>
+      <c r="J10" s="164"/>
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
       <c r="M10" s="13"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13"/>
     </row>
-    <row r="11" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="196"/>
-      <c r="B11" s="197"/>
-      <c r="C11" s="197"/>
-      <c r="D11" s="197"/>
-      <c r="E11" s="197"/>
-      <c r="F11" s="197"/>
-      <c r="G11" s="197"/>
-      <c r="H11" s="197"/>
-      <c r="I11" s="197"/>
-      <c r="J11" s="198"/>
+    <row r="11" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="165"/>
+      <c r="B11" s="166"/>
+      <c r="C11" s="166"/>
+      <c r="D11" s="166"/>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="166"/>
+      <c r="H11" s="166"/>
+      <c r="I11" s="166"/>
+      <c r="J11" s="167"/>
       <c r="K11" s="14"/>
       <c r="L11" s="14"/>
       <c r="M11" s="14"/>
       <c r="N11" s="14"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="1:15" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="15"/>
@@ -8810,7 +8819,7 @@
       <c r="I12" s="17"/>
       <c r="J12" s="134"/>
     </row>
-    <row r="13" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>3</v>
       </c>
@@ -8821,26 +8830,26 @@
       <c r="D13" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="E13" s="224" t="s">
+      <c r="E13" s="212" t="s">
         <v>428</v>
       </c>
-      <c r="F13" s="221" t="s">
+      <c r="F13" s="209" t="s">
         <v>6</v>
       </c>
-      <c r="G13" s="222"/>
-      <c r="H13" s="222"/>
-      <c r="I13" s="223"/>
+      <c r="G13" s="210"/>
+      <c r="H13" s="210"/>
+      <c r="I13" s="211"/>
       <c r="J13" s="22" t="s">
         <v>7</v>
       </c>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" spans="1:15" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="33" x14ac:dyDescent="0.25">
       <c r="A14" s="20"/>
       <c r="B14" s="137"/>
       <c r="C14" s="138"/>
       <c r="D14" s="20"/>
-      <c r="E14" s="225"/>
+      <c r="E14" s="213"/>
       <c r="F14" s="139" t="s">
         <v>424</v>
       </c>
@@ -8856,14 +8865,14 @@
       <c r="J14" s="140"/>
       <c r="K14" s="126"/>
     </row>
-    <row r="15" spans="1:15" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A15" s="127" t="s">
         <v>411</v>
       </c>
-      <c r="B15" s="202" t="s">
+      <c r="B15" s="216" t="s">
         <v>412</v>
       </c>
-      <c r="C15" s="203"/>
+      <c r="C15" s="217"/>
       <c r="D15" s="128"/>
       <c r="E15" s="135" t="s">
         <v>413</v>
@@ -8883,14 +8892,14 @@
       <c r="J15" s="130"/>
       <c r="K15" s="126"/>
     </row>
-    <row r="16" spans="1:15" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="127" t="s">
         <v>414</v>
       </c>
-      <c r="B16" s="202" t="s">
+      <c r="B16" s="216" t="s">
         <v>415</v>
       </c>
-      <c r="C16" s="203"/>
+      <c r="C16" s="217"/>
       <c r="D16" s="128"/>
       <c r="E16" s="129"/>
       <c r="F16" s="129"/>
@@ -8900,114 +8909,114 @@
       <c r="J16" s="130"/>
       <c r="K16" s="126"/>
     </row>
-    <row r="17" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="209">
+    <row r="17" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="219">
         <f>IF(LEN(C17)=0,"",COUNTA($C$17:C17))</f>
         <v>1</v>
       </c>
-      <c r="B17" s="160" t="s">
+      <c r="B17" s="170" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="212" t="s">
+      <c r="C17" s="222" t="s">
         <v>9</v>
       </c>
       <c r="D17" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="155">
+      <c r="E17" s="199">
         <v>185738</v>
       </c>
-      <c r="F17" s="155" t="s">
+      <c r="F17" s="199" t="s">
         <v>429</v>
       </c>
-      <c r="G17" s="155" t="s">
+      <c r="G17" s="199" t="s">
         <v>429</v>
       </c>
-      <c r="H17" s="155" t="s">
+      <c r="H17" s="199" t="s">
         <v>429</v>
       </c>
-      <c r="I17" s="155" t="s">
+      <c r="I17" s="199" t="s">
         <v>429</v>
       </c>
-      <c r="J17" s="206"/>
+      <c r="J17" s="226"/>
       <c r="K17" s="26"/>
     </row>
-    <row r="18" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="210"/>
-      <c r="B18" s="161"/>
-      <c r="C18" s="213"/>
+    <row r="18" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="220"/>
+      <c r="B18" s="171"/>
+      <c r="C18" s="223"/>
       <c r="D18" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E18" s="156"/>
-      <c r="F18" s="156"/>
-      <c r="G18" s="156"/>
-      <c r="H18" s="156"/>
-      <c r="I18" s="156"/>
-      <c r="J18" s="207"/>
+      <c r="E18" s="200"/>
+      <c r="F18" s="200"/>
+      <c r="G18" s="200"/>
+      <c r="H18" s="200"/>
+      <c r="I18" s="200"/>
+      <c r="J18" s="227"/>
       <c r="K18" s="26"/>
     </row>
-    <row r="19" spans="1:11" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="210"/>
-      <c r="B19" s="161"/>
-      <c r="C19" s="213"/>
+    <row r="19" spans="1:11" ht="33" x14ac:dyDescent="0.25">
+      <c r="A19" s="220"/>
+      <c r="B19" s="171"/>
+      <c r="C19" s="223"/>
       <c r="D19" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E19" s="156"/>
-      <c r="F19" s="156"/>
-      <c r="G19" s="156"/>
-      <c r="H19" s="156"/>
-      <c r="I19" s="156"/>
-      <c r="J19" s="207"/>
+      <c r="E19" s="200"/>
+      <c r="F19" s="200"/>
+      <c r="G19" s="200"/>
+      <c r="H19" s="200"/>
+      <c r="I19" s="200"/>
+      <c r="J19" s="227"/>
       <c r="K19" s="26"/>
     </row>
-    <row r="20" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="210"/>
-      <c r="B20" s="161"/>
-      <c r="C20" s="213"/>
+    <row r="20" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="220"/>
+      <c r="B20" s="171"/>
+      <c r="C20" s="223"/>
       <c r="D20" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E20" s="156"/>
-      <c r="F20" s="156"/>
-      <c r="G20" s="156"/>
-      <c r="H20" s="156"/>
-      <c r="I20" s="156"/>
-      <c r="J20" s="207"/>
+      <c r="E20" s="200"/>
+      <c r="F20" s="200"/>
+      <c r="G20" s="200"/>
+      <c r="H20" s="200"/>
+      <c r="I20" s="200"/>
+      <c r="J20" s="227"/>
       <c r="K20" s="27"/>
     </row>
-    <row r="21" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="210"/>
-      <c r="B21" s="161"/>
-      <c r="C21" s="213"/>
+    <row r="21" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="220"/>
+      <c r="B21" s="171"/>
+      <c r="C21" s="223"/>
       <c r="D21" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E21" s="156"/>
-      <c r="F21" s="156"/>
-      <c r="G21" s="156"/>
-      <c r="H21" s="156"/>
-      <c r="I21" s="156"/>
-      <c r="J21" s="207"/>
+      <c r="E21" s="200"/>
+      <c r="F21" s="200"/>
+      <c r="G21" s="200"/>
+      <c r="H21" s="200"/>
+      <c r="I21" s="200"/>
+      <c r="J21" s="227"/>
       <c r="K21" s="27"/>
     </row>
-    <row r="22" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="211"/>
-      <c r="B22" s="162"/>
-      <c r="C22" s="214"/>
+    <row r="22" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="221"/>
+      <c r="B22" s="172"/>
+      <c r="C22" s="224"/>
       <c r="D22" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E22" s="157"/>
-      <c r="F22" s="157"/>
-      <c r="G22" s="157"/>
-      <c r="H22" s="157"/>
-      <c r="I22" s="157"/>
-      <c r="J22" s="208"/>
+      <c r="E22" s="201"/>
+      <c r="F22" s="201"/>
+      <c r="G22" s="201"/>
+      <c r="H22" s="201"/>
+      <c r="I22" s="201"/>
+      <c r="J22" s="228"/>
       <c r="K22" s="27"/>
     </row>
-    <row r="23" spans="1:11" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="33" x14ac:dyDescent="0.25">
       <c r="A23" s="29">
         <f>IF(LEN(C23)=0,"",COUNTA($C$17:C23))</f>
         <v>2</v>
@@ -9033,7 +9042,7 @@
       <c r="J23" s="34"/>
       <c r="K23" s="27"/>
     </row>
-    <row r="24" spans="1:11" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="33" x14ac:dyDescent="0.25">
       <c r="A24" s="29">
         <f>IF(LEN(C24)=0,"",COUNTA($C$17:C24))</f>
         <v>3</v>
@@ -9059,14 +9068,14 @@
       <c r="J24" s="34"/>
       <c r="K24" s="27"/>
     </row>
-    <row r="25" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="127" t="s">
         <v>416</v>
       </c>
-      <c r="B25" s="202" t="s">
+      <c r="B25" s="216" t="s">
         <v>417</v>
       </c>
-      <c r="C25" s="203"/>
+      <c r="C25" s="217"/>
       <c r="D25" s="128"/>
       <c r="E25" s="129"/>
       <c r="F25" s="129"/>
@@ -9076,7 +9085,7 @@
       <c r="J25" s="130"/>
       <c r="K25" s="126"/>
     </row>
-    <row r="26" spans="1:11" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="66" x14ac:dyDescent="0.25">
       <c r="A26" s="29">
         <f>IF(LEN(C26)=0,"",COUNTA($C$17:C26))</f>
         <v>4</v>
@@ -9108,7 +9117,7 @@
       <c r="J26" s="34"/>
       <c r="K26" s="27"/>
     </row>
-    <row r="27" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A27" s="29">
         <f>IF(LEN(C27)=0,"",COUNTA($C$17:C27))</f>
         <v>5</v>
@@ -9140,7 +9149,7 @@
       <c r="J27" s="34"/>
       <c r="K27" s="27"/>
     </row>
-    <row r="28" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="29">
         <f>IF(LEN(C28)=0,"",COUNTA($C$17:C28))</f>
         <v>6</v>
@@ -9172,19 +9181,19 @@
       <c r="J28" s="34"/>
       <c r="K28" s="27"/>
     </row>
-    <row r="29" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A29" s="29">
         <f>IF(LEN(C29)=0,"",COUNTA($C$17:C29))</f>
         <v>7</v>
       </c>
-      <c r="B29" s="160" t="s">
+      <c r="B29" s="170" t="s">
         <v>410</v>
       </c>
       <c r="C29" s="24" t="s">
         <v>387</v>
       </c>
       <c r="D29" s="24"/>
-      <c r="E29" s="155">
+      <c r="E29" s="199">
         <v>91500</v>
       </c>
       <c r="F29" s="33" t="s">
@@ -9193,83 +9202,83 @@
       <c r="G29" s="33" t="s">
         <v>429</v>
       </c>
-      <c r="H29" s="215"/>
-      <c r="I29" s="215"/>
-      <c r="J29" s="168"/>
+      <c r="H29" s="204"/>
+      <c r="I29" s="204"/>
+      <c r="J29" s="178"/>
       <c r="K29" s="27"/>
     </row>
-    <row r="30" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A30" s="29">
         <f>IF(LEN(C30)=0,"",COUNTA($C$17:C30))</f>
         <v>8</v>
       </c>
-      <c r="B30" s="161"/>
+      <c r="B30" s="171"/>
       <c r="C30" s="24" t="s">
         <v>388</v>
       </c>
       <c r="D30" s="24"/>
-      <c r="E30" s="156"/>
+      <c r="E30" s="200"/>
       <c r="F30" s="33" t="s">
         <v>429</v>
       </c>
       <c r="G30" s="33" t="s">
         <v>429</v>
       </c>
-      <c r="H30" s="216"/>
-      <c r="I30" s="216"/>
-      <c r="J30" s="201"/>
+      <c r="H30" s="205"/>
+      <c r="I30" s="205"/>
+      <c r="J30" s="225"/>
       <c r="K30" s="27"/>
     </row>
-    <row r="31" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A31" s="29">
         <f>IF(LEN(C31)=0,"",COUNTA($C$17:C31))</f>
         <v>9</v>
       </c>
-      <c r="B31" s="161"/>
+      <c r="B31" s="171"/>
       <c r="C31" s="24" t="s">
         <v>389</v>
       </c>
       <c r="D31" s="24"/>
-      <c r="E31" s="156"/>
+      <c r="E31" s="200"/>
       <c r="F31" s="33" t="s">
         <v>429</v>
       </c>
       <c r="G31" s="33" t="s">
         <v>429</v>
       </c>
-      <c r="H31" s="216"/>
-      <c r="I31" s="216"/>
-      <c r="J31" s="201"/>
+      <c r="H31" s="205"/>
+      <c r="I31" s="205"/>
+      <c r="J31" s="225"/>
       <c r="K31" s="27"/>
     </row>
-    <row r="32" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A32" s="29">
         <f>IF(LEN(C32)=0,"",COUNTA($C$17:C32))</f>
         <v>10</v>
       </c>
-      <c r="B32" s="162"/>
+      <c r="B32" s="172"/>
       <c r="C32" s="31" t="s">
         <v>390</v>
       </c>
       <c r="D32" s="24"/>
-      <c r="E32" s="157"/>
+      <c r="E32" s="201"/>
       <c r="F32" s="33" t="s">
         <v>429</v>
       </c>
       <c r="G32" s="33" t="s">
         <v>429</v>
       </c>
-      <c r="H32" s="217"/>
-      <c r="I32" s="217"/>
-      <c r="J32" s="169"/>
+      <c r="H32" s="206"/>
+      <c r="I32" s="206"/>
+      <c r="J32" s="179"/>
       <c r="K32" s="27"/>
     </row>
-    <row r="33" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="29">
         <f>IF(LEN(C33)=0,"",COUNTA($C$17:C33))</f>
         <v>11</v>
       </c>
-      <c r="B33" s="163" t="s">
+      <c r="B33" s="195" t="s">
         <v>28</v>
       </c>
       <c r="C33" s="35" t="s">
@@ -9278,7 +9287,7 @@
       <c r="D33" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="E33" s="204">
+      <c r="E33" s="207">
         <v>14084</v>
       </c>
       <c r="F33" s="33" t="s">
@@ -9293,24 +9302,24 @@
       <c r="I33" s="33" t="s">
         <v>429</v>
       </c>
-      <c r="J33" s="179" t="s">
+      <c r="J33" s="148" t="s">
         <v>31</v>
       </c>
       <c r="K33" s="27"/>
     </row>
-    <row r="34" spans="1:11" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" ht="33" x14ac:dyDescent="0.25">
       <c r="A34" s="29">
         <f>IF(LEN(C34)=0,"",COUNTA($C$17:C34))</f>
         <v>12</v>
       </c>
-      <c r="B34" s="163"/>
+      <c r="B34" s="195"/>
       <c r="C34" s="35" t="s">
         <v>32</v>
       </c>
       <c r="D34" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="E34" s="205"/>
+      <c r="E34" s="208"/>
       <c r="F34" s="33" t="s">
         <v>429</v>
       </c>
@@ -9323,10 +9332,10 @@
       <c r="I34" s="33" t="s">
         <v>429</v>
       </c>
-      <c r="J34" s="180"/>
+      <c r="J34" s="149"/>
       <c r="K34" s="27"/>
     </row>
-    <row r="35" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A35" s="29">
         <f>IF(LEN(C35)=0,"",COUNTA($C$17:C35))</f>
         <v>13</v>
@@ -9358,12 +9367,12 @@
       <c r="J35" s="34"/>
       <c r="K35" s="27"/>
     </row>
-    <row r="36" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="29">
         <f>IF(LEN(C36)=0,"",COUNTA($C$17:C36))</f>
         <v>14</v>
       </c>
-      <c r="B36" s="178"/>
+      <c r="B36" s="191"/>
       <c r="C36" s="35" t="s">
         <v>56</v>
       </c>
@@ -9385,15 +9394,15 @@
       <c r="I36" s="33" t="s">
         <v>429</v>
       </c>
-      <c r="J36" s="153"/>
+      <c r="J36" s="174"/>
       <c r="K36" s="27"/>
     </row>
-    <row r="37" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="29">
         <f>IF(LEN(C37)=0,"",COUNTA($C$17:C37))</f>
         <v>15</v>
       </c>
-      <c r="B37" s="178"/>
+      <c r="B37" s="191"/>
       <c r="C37" s="35" t="s">
         <v>60</v>
       </c>
@@ -9415,10 +9424,10 @@
       <c r="I37" s="33" t="s">
         <v>429</v>
       </c>
-      <c r="J37" s="154"/>
+      <c r="J37" s="175"/>
       <c r="K37" s="27"/>
     </row>
-    <row r="38" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A38" s="29">
         <f>IF(LEN(C38)=0,"",COUNTA($C$17:C38))</f>
         <v>16</v>
@@ -9448,7 +9457,7 @@
       <c r="J38" s="34"/>
       <c r="K38" s="27"/>
     </row>
-    <row r="39" spans="1:11" s="52" customFormat="1" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" s="52" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A39" s="29">
         <f>IF(LEN(C39)=0,"",COUNTA($C$17:C39))</f>
         <v>17</v>
@@ -9478,7 +9487,7 @@
       <c r="J39" s="34"/>
       <c r="K39" s="51"/>
     </row>
-    <row r="40" spans="1:11" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" ht="33" x14ac:dyDescent="0.25">
       <c r="A40" s="29">
         <f>IF(LEN(C40)=0,"",COUNTA($C$17:C40))</f>
         <v>18</v>
@@ -9504,14 +9513,14 @@
       <c r="J40" s="34"/>
       <c r="K40" s="27"/>
     </row>
-    <row r="41" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="127" t="s">
         <v>416</v>
       </c>
-      <c r="B41" s="202" t="s">
+      <c r="B41" s="216" t="s">
         <v>418</v>
       </c>
-      <c r="C41" s="203"/>
+      <c r="C41" s="217"/>
       <c r="D41" s="128"/>
       <c r="E41" s="129"/>
       <c r="F41" s="129"/>
@@ -9521,7 +9530,7 @@
       <c r="J41" s="130"/>
       <c r="K41" s="126"/>
     </row>
-    <row r="42" spans="1:11" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" ht="33" x14ac:dyDescent="0.25">
       <c r="A42" s="29">
         <f>IF(LEN(C42)=0,"",COUNTA($C$17:C42))</f>
         <v>19</v>
@@ -9553,7 +9562,7 @@
       <c r="J42" s="34"/>
       <c r="K42" s="27"/>
     </row>
-    <row r="43" spans="1:11" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" ht="33" x14ac:dyDescent="0.25">
       <c r="A43" s="29">
         <f>IF(LEN(C43)=0,"",COUNTA($C$17:C43))</f>
         <v>20</v>
@@ -9577,7 +9586,7 @@
       <c r="J43" s="34"/>
       <c r="K43" s="27"/>
     </row>
-    <row r="44" spans="1:11" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" ht="33" x14ac:dyDescent="0.25">
       <c r="A44" s="29">
         <f>IF(LEN(C44)=0,"",COUNTA($C$17:C44))</f>
         <v>21</v>
@@ -9607,12 +9616,12 @@
       <c r="J44" s="34"/>
       <c r="K44" s="27"/>
     </row>
-    <row r="45" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A45" s="29">
         <f>IF(LEN(C45)=0,"",COUNTA($C$17:C45))</f>
         <v>22</v>
       </c>
-      <c r="B45" s="158" t="s">
+      <c r="B45" s="193" t="s">
         <v>209</v>
       </c>
       <c r="C45" s="31" t="s">
@@ -9639,12 +9648,12 @@
       <c r="J45" s="34"/>
       <c r="K45" s="27"/>
     </row>
-    <row r="46" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A46" s="29">
         <f>IF(LEN(C46)=0,"",COUNTA($C$17:C46))</f>
         <v>23</v>
       </c>
-      <c r="B46" s="159"/>
+      <c r="B46" s="194"/>
       <c r="C46" s="31" t="s">
         <v>212</v>
       </c>
@@ -9665,12 +9674,12 @@
       <c r="J46" s="34"/>
       <c r="K46" s="27"/>
     </row>
-    <row r="47" spans="1:11" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" ht="33" x14ac:dyDescent="0.25">
       <c r="A47" s="29">
         <f>IF(LEN(C47)=0,"",COUNTA($C$17:C47))</f>
         <v>24</v>
       </c>
-      <c r="B47" s="220"/>
+      <c r="B47" s="215"/>
       <c r="C47" s="31" t="s">
         <v>214</v>
       </c>
@@ -9695,7 +9704,7 @@
       <c r="J47" s="34"/>
       <c r="K47" s="27"/>
     </row>
-    <row r="48" spans="1:11" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" ht="33" x14ac:dyDescent="0.25">
       <c r="A48" s="29">
         <f>IF(LEN(C48)=0,"",COUNTA($C$17:C48))</f>
         <v>25</v>
@@ -9723,7 +9732,7 @@
       <c r="J48" s="34"/>
       <c r="K48" s="27"/>
     </row>
-    <row r="49" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A49" s="29">
         <f>IF(LEN(C49)=0,"",COUNTA($C$17:C49))</f>
         <v>26</v>
@@ -9753,34 +9762,34 @@
       <c r="J49" s="34"/>
       <c r="K49" s="27"/>
     </row>
-    <row r="50" spans="1:11" s="231" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="226" t="s">
+    <row r="50" spans="1:11" s="145" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A50" s="229" t="s">
         <v>38</v>
       </c>
-      <c r="B50" s="227"/>
-      <c r="C50" s="227"/>
-      <c r="D50" s="228"/>
-      <c r="E50" s="229"/>
-      <c r="F50" s="229">
+      <c r="B50" s="230"/>
+      <c r="C50" s="230"/>
+      <c r="D50" s="231"/>
+      <c r="E50" s="143"/>
+      <c r="F50" s="143">
         <f>SUMIF(F17:F49,"x",$E$17:$E$49)</f>
         <v>813782</v>
       </c>
-      <c r="G50" s="229">
+      <c r="G50" s="143">
         <f t="shared" ref="G50:I50" si="0">SUMIF(G17:G49,"x",$E$17:$E$49)</f>
         <v>752121</v>
       </c>
-      <c r="H50" s="229">
+      <c r="H50" s="143">
         <f t="shared" si="0"/>
         <v>822072</v>
       </c>
-      <c r="I50" s="229">
+      <c r="I50" s="143">
         <f t="shared" si="0"/>
         <v>822072</v>
       </c>
       <c r="J50" s="41"/>
-      <c r="K50" s="230"/>
-    </row>
-    <row r="51" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="K50" s="144"/>
+    </row>
+    <row r="51" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A51" s="42"/>
       <c r="B51" s="43"/>
       <c r="C51" s="44"/>
@@ -9793,13 +9802,13 @@
       <c r="J51" s="46"/>
       <c r="K51" s="27"/>
     </row>
-    <row r="52" spans="1:11" s="110" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="146" t="s">
+    <row r="52" spans="1:11" s="110" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A52" s="196" t="s">
         <v>396</v>
       </c>
-      <c r="B52" s="146"/>
-      <c r="C52" s="146"/>
-      <c r="D52" s="146"/>
+      <c r="B52" s="196"/>
+      <c r="C52" s="196"/>
+      <c r="D52" s="196"/>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
       <c r="G52" s="7"/>
@@ -9807,77 +9816,77 @@
       <c r="I52" s="7"/>
       <c r="J52" s="109"/>
     </row>
-    <row r="53" spans="1:11" s="110" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" s="110" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A53" s="111"/>
-      <c r="B53" s="143" t="s">
+      <c r="B53" s="202" t="s">
         <v>397</v>
       </c>
-      <c r="C53" s="143"/>
-      <c r="D53" s="143"/>
-      <c r="E53" s="143"/>
-      <c r="F53" s="143"/>
-      <c r="G53" s="143"/>
-      <c r="H53" s="143"/>
-      <c r="I53" s="143"/>
-      <c r="J53" s="143"/>
-    </row>
-    <row r="54" spans="1:11" s="110" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="C53" s="202"/>
+      <c r="D53" s="202"/>
+      <c r="E53" s="202"/>
+      <c r="F53" s="202"/>
+      <c r="G53" s="202"/>
+      <c r="H53" s="202"/>
+      <c r="I53" s="202"/>
+      <c r="J53" s="202"/>
+    </row>
+    <row r="54" spans="1:11" s="110" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A54" s="111"/>
-      <c r="B54" s="143" t="s">
+      <c r="B54" s="202" t="s">
         <v>398</v>
       </c>
-      <c r="C54" s="143"/>
-      <c r="D54" s="143"/>
-      <c r="E54" s="143"/>
-      <c r="F54" s="143"/>
-      <c r="G54" s="143"/>
-      <c r="H54" s="143"/>
-      <c r="I54" s="143"/>
-      <c r="J54" s="143"/>
-    </row>
-    <row r="55" spans="1:11" s="113" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C54" s="202"/>
+      <c r="D54" s="202"/>
+      <c r="E54" s="202"/>
+      <c r="F54" s="202"/>
+      <c r="G54" s="202"/>
+      <c r="H54" s="202"/>
+      <c r="I54" s="202"/>
+      <c r="J54" s="202"/>
+    </row>
+    <row r="55" spans="1:11" s="113" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="112"/>
-      <c r="B55" s="143" t="s">
+      <c r="B55" s="202" t="s">
         <v>399</v>
       </c>
-      <c r="C55" s="143"/>
-      <c r="D55" s="143"/>
-      <c r="E55" s="143"/>
-      <c r="F55" s="143"/>
-      <c r="G55" s="143"/>
-      <c r="H55" s="143"/>
-      <c r="I55" s="143"/>
-      <c r="J55" s="143"/>
-    </row>
-    <row r="56" spans="1:11" s="115" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C55" s="202"/>
+      <c r="D55" s="202"/>
+      <c r="E55" s="202"/>
+      <c r="F55" s="202"/>
+      <c r="G55" s="202"/>
+      <c r="H55" s="202"/>
+      <c r="I55" s="202"/>
+      <c r="J55" s="202"/>
+    </row>
+    <row r="56" spans="1:11" s="115" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="114"/>
-      <c r="B56" s="144" t="s">
+      <c r="B56" s="203" t="s">
         <v>400</v>
       </c>
-      <c r="C56" s="144"/>
-      <c r="D56" s="144"/>
-      <c r="E56" s="144"/>
-      <c r="F56" s="144"/>
-      <c r="G56" s="144"/>
-      <c r="H56" s="144"/>
-      <c r="I56" s="144"/>
-      <c r="J56" s="144"/>
-    </row>
-    <row r="57" spans="1:11" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C56" s="203"/>
+      <c r="D56" s="203"/>
+      <c r="E56" s="203"/>
+      <c r="F56" s="203"/>
+      <c r="G56" s="203"/>
+      <c r="H56" s="203"/>
+      <c r="I56" s="203"/>
+      <c r="J56" s="203"/>
+    </row>
+    <row r="57" spans="1:11" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="109"/>
-      <c r="B57" s="143" t="s">
+      <c r="B57" s="202" t="s">
         <v>401</v>
       </c>
-      <c r="C57" s="143"/>
-      <c r="D57" s="143"/>
-      <c r="E57" s="143"/>
-      <c r="F57" s="143"/>
-      <c r="G57" s="143"/>
-      <c r="H57" s="143"/>
-      <c r="I57" s="143"/>
-      <c r="J57" s="143"/>
-    </row>
-    <row r="58" spans="1:11" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="C57" s="202"/>
+      <c r="D57" s="202"/>
+      <c r="E57" s="202"/>
+      <c r="F57" s="202"/>
+      <c r="G57" s="202"/>
+      <c r="H57" s="202"/>
+      <c r="I57" s="202"/>
+      <c r="J57" s="202"/>
+    </row>
+    <row r="58" spans="1:11" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A58" s="109"/>
       <c r="B58" s="112" t="s">
         <v>402</v>
@@ -9891,7 +9900,7 @@
       <c r="I58" s="7"/>
       <c r="J58" s="5"/>
     </row>
-    <row r="59" spans="1:11" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A59" s="109"/>
       <c r="B59" s="112" t="s">
         <v>403</v>
@@ -9905,7 +9914,7 @@
       <c r="I59" s="7"/>
       <c r="J59" s="5"/>
     </row>
-    <row r="60" spans="1:11" s="121" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" s="121" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A60" s="117" t="s">
         <v>404</v>
       </c>
@@ -9919,7 +9928,7 @@
       <c r="I60" s="119"/>
       <c r="J60" s="120"/>
     </row>
-    <row r="61" spans="1:11" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A61" s="109"/>
       <c r="B61" s="5" t="s">
         <v>405</v>
@@ -9935,7 +9944,7 @@
       <c r="I61" s="10"/>
       <c r="J61" s="5"/>
     </row>
-    <row r="62" spans="1:11" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A62" s="109"/>
       <c r="B62" s="5" t="s">
         <v>407</v>
@@ -9949,7 +9958,7 @@
       <c r="I62" s="10"/>
       <c r="J62" s="5"/>
     </row>
-    <row r="63" spans="1:11" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A63" s="109"/>
       <c r="B63" s="5" t="s">
         <v>408</v>
@@ -9965,16 +9974,25 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="B53:J53"/>
-    <mergeCell ref="B54:J54"/>
-    <mergeCell ref="B55:J55"/>
-    <mergeCell ref="B56:J56"/>
-    <mergeCell ref="B57:J57"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="E17:E22"/>
+    <mergeCell ref="D1:J5"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="B9:J9"/>
+    <mergeCell ref="A10:J11"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="A17:A22"/>
+    <mergeCell ref="B17:B22"/>
+    <mergeCell ref="C17:C22"/>
+    <mergeCell ref="F17:F22"/>
+    <mergeCell ref="G17:G22"/>
+    <mergeCell ref="H17:H22"/>
+    <mergeCell ref="I17:I22"/>
+    <mergeCell ref="J17:J22"/>
     <mergeCell ref="A52:D52"/>
     <mergeCell ref="J29:J32"/>
     <mergeCell ref="B33:B34"/>
@@ -9984,25 +10002,16 @@
     <mergeCell ref="E29:E32"/>
     <mergeCell ref="H29:H32"/>
     <mergeCell ref="I29:I32"/>
-    <mergeCell ref="F17:F22"/>
-    <mergeCell ref="G17:G22"/>
-    <mergeCell ref="H17:H22"/>
-    <mergeCell ref="I17:I22"/>
-    <mergeCell ref="J17:J22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="A17:A22"/>
-    <mergeCell ref="B17:B22"/>
-    <mergeCell ref="C17:C22"/>
-    <mergeCell ref="E17:E22"/>
-    <mergeCell ref="D1:J5"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="B9:J9"/>
-    <mergeCell ref="A10:J11"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="B53:J53"/>
+    <mergeCell ref="B54:J54"/>
+    <mergeCell ref="B55:J55"/>
+    <mergeCell ref="B56:J56"/>
+    <mergeCell ref="B57:J57"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -10012,62 +10021,62 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0BEB68B-8A7B-40D8-A3E4-B30A5672B5C2}">
   <dimension ref="A1:K48"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="19" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" style="122" customWidth="1"/>
-    <col min="3" max="3" width="53.33203125" style="19" customWidth="1"/>
-    <col min="4" max="4" width="48.5546875" style="19" customWidth="1"/>
-    <col min="5" max="5" width="16.44140625" style="123" customWidth="1"/>
-    <col min="6" max="6" width="28.33203125" style="124" customWidth="1"/>
-    <col min="7" max="7" width="19.6640625" style="19" customWidth="1"/>
-    <col min="8" max="8" width="9.88671875" style="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.109375" style="19"/>
+    <col min="2" max="2" width="13.42578125" style="122" customWidth="1"/>
+    <col min="3" max="3" width="53.28515625" style="19" customWidth="1"/>
+    <col min="4" max="4" width="48.5703125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" style="123" customWidth="1"/>
+    <col min="6" max="6" width="28.28515625" style="124" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" style="19" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="181" t="s">
+      <c r="D1" s="150" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="182"/>
-      <c r="F1" s="183"/>
-    </row>
-    <row r="2" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E1" s="151"/>
+      <c r="F1" s="152"/>
+    </row>
+    <row r="2" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="181"/>
-      <c r="E2" s="182"/>
-      <c r="F2" s="183"/>
-    </row>
-    <row r="3" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D2" s="150"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="152"/>
+    </row>
+    <row r="3" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="181"/>
-      <c r="E3" s="182"/>
-      <c r="F3" s="183"/>
-    </row>
-    <row r="4" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D3" s="150"/>
+      <c r="E3" s="151"/>
+      <c r="F3" s="152"/>
+    </row>
+    <row r="4" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="181"/>
-      <c r="E4" s="182"/>
-      <c r="F4" s="183"/>
-    </row>
-    <row r="5" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D4" s="150"/>
+      <c r="E4" s="151"/>
+      <c r="F4" s="152"/>
+    </row>
+    <row r="5" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="184"/>
-      <c r="E5" s="185"/>
-      <c r="F5" s="186"/>
-    </row>
-    <row r="6" spans="1:11" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="D5" s="153"/>
+      <c r="E5" s="154"/>
+      <c r="F5" s="155"/>
+    </row>
+    <row r="6" spans="1:11" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -10075,22 +10084,22 @@
       <c r="E6" s="7"/>
       <c r="F6" s="5"/>
     </row>
-    <row r="7" spans="1:11" s="4" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A7" s="187" t="s">
+    <row r="7" spans="1:11" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="156" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="188"/>
-      <c r="C7" s="188"/>
-      <c r="D7" s="188"/>
-      <c r="E7" s="188"/>
-      <c r="F7" s="189"/>
+      <c r="B7" s="157"/>
+      <c r="C7" s="157"/>
+      <c r="D7" s="157"/>
+      <c r="E7" s="157"/>
+      <c r="F7" s="158"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
     </row>
-    <row r="8" spans="1:11" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -10103,49 +10112,49 @@
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
     </row>
-    <row r="9" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
-      <c r="B9" s="190" t="s">
+      <c r="B9" s="159" t="s">
         <v>409</v>
       </c>
-      <c r="C9" s="191"/>
-      <c r="D9" s="191"/>
-      <c r="E9" s="191"/>
-      <c r="F9" s="192"/>
+      <c r="C9" s="160"/>
+      <c r="D9" s="160"/>
+      <c r="E9" s="160"/>
+      <c r="F9" s="161"/>
       <c r="G9" s="12"/>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
     </row>
-    <row r="10" spans="1:11" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="193" t="s">
+    <row r="10" spans="1:11" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="162" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="194"/>
-      <c r="C10" s="194"/>
-      <c r="D10" s="194"/>
-      <c r="E10" s="194"/>
-      <c r="F10" s="195"/>
+      <c r="B10" s="163"/>
+      <c r="C10" s="163"/>
+      <c r="D10" s="163"/>
+      <c r="E10" s="163"/>
+      <c r="F10" s="164"/>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
     </row>
-    <row r="11" spans="1:11" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="196"/>
-      <c r="B11" s="197"/>
-      <c r="C11" s="197"/>
-      <c r="D11" s="197"/>
-      <c r="E11" s="197"/>
-      <c r="F11" s="198"/>
+    <row r="11" spans="1:11" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="165"/>
+      <c r="B11" s="166"/>
+      <c r="C11" s="166"/>
+      <c r="D11" s="166"/>
+      <c r="E11" s="166"/>
+      <c r="F11" s="167"/>
       <c r="G11" s="14"/>
       <c r="H11" s="14"/>
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
       <c r="K11" s="14"/>
     </row>
-    <row r="12" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="15"/>
@@ -10153,7 +10162,7 @@
       <c r="E12" s="17"/>
       <c r="F12" s="134"/>
     </row>
-    <row r="13" spans="1:11" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="33" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>3</v>
       </c>
@@ -10172,100 +10181,100 @@
       </c>
       <c r="G13" s="23"/>
     </row>
-    <row r="14" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="127" t="s">
         <v>411</v>
       </c>
-      <c r="B14" s="202" t="s">
+      <c r="B14" s="216" t="s">
         <v>420</v>
       </c>
-      <c r="C14" s="203"/>
+      <c r="C14" s="217"/>
       <c r="D14" s="128"/>
       <c r="E14" s="129"/>
       <c r="F14" s="130"/>
       <c r="G14" s="126"/>
     </row>
-    <row r="15" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="209">
+    <row r="15" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="219">
         <f>IF(LEN(C15)=0,"",COUNTA($C$15:C15))</f>
         <v>1</v>
       </c>
-      <c r="B15" s="160" t="s">
+      <c r="B15" s="170" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="212" t="s">
+      <c r="C15" s="222" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="155">
+      <c r="E15" s="199">
         <v>185738</v>
       </c>
-      <c r="F15" s="206"/>
+      <c r="F15" s="226"/>
       <c r="G15" s="26"/>
     </row>
-    <row r="16" spans="1:11" ht="50.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="210"/>
-      <c r="B16" s="161"/>
-      <c r="C16" s="213"/>
+    <row r="16" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="220"/>
+      <c r="B16" s="171"/>
+      <c r="C16" s="223"/>
       <c r="D16" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="156"/>
-      <c r="F16" s="207"/>
+      <c r="E16" s="200"/>
+      <c r="F16" s="227"/>
       <c r="G16" s="26"/>
     </row>
-    <row r="17" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="210"/>
-      <c r="B17" s="161"/>
-      <c r="C17" s="213"/>
+    <row r="17" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A17" s="220"/>
+      <c r="B17" s="171"/>
+      <c r="C17" s="223"/>
       <c r="D17" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="156"/>
-      <c r="F17" s="207"/>
+      <c r="E17" s="200"/>
+      <c r="F17" s="227"/>
       <c r="G17" s="26"/>
     </row>
-    <row r="18" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="210"/>
-      <c r="B18" s="161"/>
-      <c r="C18" s="213"/>
+    <row r="18" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="220"/>
+      <c r="B18" s="171"/>
+      <c r="C18" s="223"/>
       <c r="D18" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E18" s="156"/>
-      <c r="F18" s="207"/>
+      <c r="E18" s="200"/>
+      <c r="F18" s="227"/>
       <c r="G18" s="27"/>
     </row>
-    <row r="19" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="210"/>
-      <c r="B19" s="161"/>
-      <c r="C19" s="213"/>
+    <row r="19" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="220"/>
+      <c r="B19" s="171"/>
+      <c r="C19" s="223"/>
       <c r="D19" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="156"/>
-      <c r="F19" s="207"/>
+      <c r="E19" s="200"/>
+      <c r="F19" s="227"/>
       <c r="G19" s="27"/>
     </row>
-    <row r="20" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="211"/>
-      <c r="B20" s="162"/>
-      <c r="C20" s="214"/>
+    <row r="20" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="221"/>
+      <c r="B20" s="172"/>
+      <c r="C20" s="224"/>
       <c r="D20" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="157"/>
-      <c r="F20" s="208"/>
+      <c r="E20" s="201"/>
+      <c r="F20" s="228"/>
       <c r="G20" s="27"/>
     </row>
-    <row r="21" spans="1:7" s="95" customFormat="1" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" s="95" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A21" s="29">
         <f>IF(LEN(C21)=0,"",COUNTA($C$15:C21))</f>
         <v>2</v>
       </c>
-      <c r="B21" s="160" t="s">
+      <c r="B21" s="170" t="s">
         <v>316</v>
       </c>
       <c r="C21" s="24" t="s">
@@ -10279,12 +10288,12 @@
       </c>
       <c r="F21" s="34"/>
     </row>
-    <row r="22" spans="1:7" s="95" customFormat="1" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" s="95" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A22" s="29">
         <f>IF(LEN(C22)=0,"",COUNTA($C$15:C22))</f>
         <v>3</v>
       </c>
-      <c r="B22" s="161"/>
+      <c r="B22" s="171"/>
       <c r="C22" s="24" t="s">
         <v>319</v>
       </c>
@@ -10296,12 +10305,12 @@
       </c>
       <c r="F22" s="34"/>
     </row>
-    <row r="23" spans="1:7" s="95" customFormat="1" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" s="95" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A23" s="29">
         <f>IF(LEN(C23)=0,"",COUNTA($C$15:C23))</f>
         <v>4</v>
       </c>
-      <c r="B23" s="162"/>
+      <c r="B23" s="172"/>
       <c r="C23" s="24" t="s">
         <v>421</v>
       </c>
@@ -10311,7 +10320,7 @@
       </c>
       <c r="F23" s="34"/>
     </row>
-    <row r="24" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A24" s="29">
         <f>IF(LEN(C24)=0,"",COUNTA($C$15:C24))</f>
         <v>5</v>
@@ -10331,7 +10340,7 @@
       <c r="F24" s="34"/>
       <c r="G24" s="27"/>
     </row>
-    <row r="25" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A25" s="29">
         <f>IF(LEN(C25)=0,"",COUNTA($C$15:C25))</f>
         <v>6</v>
@@ -10351,7 +10360,7 @@
       <c r="F25" s="34"/>
       <c r="G25" s="27"/>
     </row>
-    <row r="26" spans="1:7" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="29">
         <f>IF(LEN(C26)=0,"",COUNTA($C$15:C26))</f>
         <v>7</v>
@@ -10371,12 +10380,12 @@
       <c r="F26" s="34"/>
       <c r="G26" s="27"/>
     </row>
-    <row r="27" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="29">
         <f>IF(LEN(C27)=0,"",COUNTA($C$15:C27))</f>
         <v>8</v>
       </c>
-      <c r="B27" s="163" t="s">
+      <c r="B27" s="195" t="s">
         <v>28</v>
       </c>
       <c r="C27" s="35" t="s">
@@ -10385,31 +10394,31 @@
       <c r="D27" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="E27" s="204">
+      <c r="E27" s="207">
         <v>14084</v>
       </c>
-      <c r="F27" s="152" t="s">
+      <c r="F27" s="173" t="s">
         <v>31</v>
       </c>
       <c r="G27" s="27"/>
     </row>
-    <row r="28" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A28" s="29">
         <f>IF(LEN(C28)=0,"",COUNTA($C$15:C28))</f>
         <v>9</v>
       </c>
-      <c r="B28" s="163"/>
+      <c r="B28" s="195"/>
       <c r="C28" s="35" t="s">
         <v>32</v>
       </c>
       <c r="D28" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="E28" s="205"/>
-      <c r="F28" s="154"/>
+      <c r="E28" s="208"/>
+      <c r="F28" s="175"/>
       <c r="G28" s="27"/>
     </row>
-    <row r="29" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A29" s="29">
         <f>IF(LEN(C29)=0,"",COUNTA($C$15:C29))</f>
         <v>10</v>
@@ -10429,12 +10438,12 @@
       <c r="F29" s="34"/>
       <c r="G29" s="27"/>
     </row>
-    <row r="30" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="29">
         <f>IF(LEN(C30)=0,"",COUNTA($C$15:C30))</f>
         <v>11</v>
       </c>
-      <c r="B30" s="178"/>
+      <c r="B30" s="191"/>
       <c r="C30" s="35" t="s">
         <v>56</v>
       </c>
@@ -10444,15 +10453,15 @@
       <c r="E30" s="67">
         <v>20604</v>
       </c>
-      <c r="F30" s="153"/>
+      <c r="F30" s="174"/>
       <c r="G30" s="27"/>
     </row>
-    <row r="31" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="29">
         <f>IF(LEN(C31)=0,"",COUNTA($C$15:C31))</f>
         <v>12</v>
       </c>
-      <c r="B31" s="178"/>
+      <c r="B31" s="191"/>
       <c r="C31" s="35" t="s">
         <v>60</v>
       </c>
@@ -10462,10 +10471,10 @@
       <c r="E31" s="67">
         <v>7289</v>
       </c>
-      <c r="F31" s="154"/>
+      <c r="F31" s="175"/>
       <c r="G31" s="27"/>
     </row>
-    <row r="32" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A32" s="29">
         <f>IF(LEN(C32)=0,"",COUNTA($C$15:C32))</f>
         <v>13</v>
@@ -10485,7 +10494,7 @@
       <c r="F32" s="34"/>
       <c r="G32" s="27"/>
     </row>
-    <row r="33" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A33" s="29">
         <f>IF(LEN(C33)=0,"",COUNTA($C$15:C33))</f>
         <v>14</v>
@@ -10501,7 +10510,7 @@
       <c r="F33" s="34"/>
       <c r="G33" s="27"/>
     </row>
-    <row r="34" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A34" s="29">
         <f>IF(LEN(C34)=0,"",COUNTA($C$15:C34))</f>
         <v>15</v>
@@ -10517,21 +10526,21 @@
       <c r="F34" s="34"/>
       <c r="G34" s="27"/>
     </row>
-    <row r="35" spans="1:7" s="231" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="226" t="s">
+    <row r="35" spans="1:7" s="145" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="229" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="227"/>
-      <c r="C35" s="227"/>
-      <c r="D35" s="228"/>
-      <c r="E35" s="229">
+      <c r="B35" s="230"/>
+      <c r="C35" s="230"/>
+      <c r="D35" s="231"/>
+      <c r="E35" s="143">
         <f>SUM(E15:E34)</f>
         <v>400609</v>
       </c>
       <c r="F35" s="41"/>
-      <c r="G35" s="230"/>
-    </row>
-    <row r="36" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="G35" s="144"/>
+    </row>
+    <row r="36" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A36" s="42"/>
       <c r="B36" s="43"/>
       <c r="C36" s="44"/>
@@ -10540,67 +10549,67 @@
       <c r="F36" s="46"/>
       <c r="G36" s="27"/>
     </row>
-    <row r="37" spans="1:7" s="110" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="146" t="s">
+    <row r="37" spans="1:7" s="110" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A37" s="196" t="s">
         <v>396</v>
       </c>
-      <c r="B37" s="146"/>
-      <c r="C37" s="146"/>
-      <c r="D37" s="146"/>
+      <c r="B37" s="196"/>
+      <c r="C37" s="196"/>
+      <c r="D37" s="196"/>
       <c r="E37" s="7"/>
       <c r="F37" s="109"/>
     </row>
-    <row r="38" spans="1:7" s="110" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" s="110" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A38" s="111"/>
-      <c r="B38" s="143" t="s">
+      <c r="B38" s="202" t="s">
         <v>397</v>
       </c>
-      <c r="C38" s="143"/>
-      <c r="D38" s="143"/>
-      <c r="E38" s="143"/>
-      <c r="F38" s="143"/>
-    </row>
-    <row r="39" spans="1:7" s="110" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="C38" s="202"/>
+      <c r="D38" s="202"/>
+      <c r="E38" s="202"/>
+      <c r="F38" s="202"/>
+    </row>
+    <row r="39" spans="1:7" s="110" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A39" s="111"/>
-      <c r="B39" s="143" t="s">
+      <c r="B39" s="202" t="s">
         <v>398</v>
       </c>
-      <c r="C39" s="143"/>
-      <c r="D39" s="143"/>
-      <c r="E39" s="143"/>
-      <c r="F39" s="143"/>
-    </row>
-    <row r="40" spans="1:7" s="113" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C39" s="202"/>
+      <c r="D39" s="202"/>
+      <c r="E39" s="202"/>
+      <c r="F39" s="202"/>
+    </row>
+    <row r="40" spans="1:7" s="113" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="112"/>
-      <c r="B40" s="143" t="s">
+      <c r="B40" s="202" t="s">
         <v>399</v>
       </c>
-      <c r="C40" s="143"/>
-      <c r="D40" s="143"/>
-      <c r="E40" s="143"/>
-      <c r="F40" s="143"/>
-    </row>
-    <row r="41" spans="1:7" s="115" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="202"/>
+      <c r="D40" s="202"/>
+      <c r="E40" s="202"/>
+      <c r="F40" s="202"/>
+    </row>
+    <row r="41" spans="1:7" s="115" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="114"/>
-      <c r="B41" s="144" t="s">
+      <c r="B41" s="203" t="s">
         <v>400</v>
       </c>
-      <c r="C41" s="144"/>
-      <c r="D41" s="144"/>
-      <c r="E41" s="144"/>
-      <c r="F41" s="144"/>
-    </row>
-    <row r="42" spans="1:7" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="203"/>
+      <c r="D41" s="203"/>
+      <c r="E41" s="203"/>
+      <c r="F41" s="203"/>
+    </row>
+    <row r="42" spans="1:7" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="109"/>
-      <c r="B42" s="143" t="s">
+      <c r="B42" s="202" t="s">
         <v>401</v>
       </c>
-      <c r="C42" s="143"/>
-      <c r="D42" s="143"/>
-      <c r="E42" s="143"/>
-      <c r="F42" s="143"/>
-    </row>
-    <row r="43" spans="1:7" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="C42" s="202"/>
+      <c r="D42" s="202"/>
+      <c r="E42" s="202"/>
+      <c r="F42" s="202"/>
+    </row>
+    <row r="43" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A43" s="109"/>
       <c r="B43" s="112" t="s">
         <v>402</v>
@@ -10610,7 +10619,7 @@
       <c r="E43" s="7"/>
       <c r="F43" s="5"/>
     </row>
-    <row r="44" spans="1:7" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A44" s="109"/>
       <c r="B44" s="112" t="s">
         <v>403</v>
@@ -10620,7 +10629,7 @@
       <c r="E44" s="7"/>
       <c r="F44" s="5"/>
     </row>
-    <row r="45" spans="1:7" s="121" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" s="121" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A45" s="117" t="s">
         <v>404</v>
       </c>
@@ -10630,7 +10639,7 @@
       <c r="E45" s="119"/>
       <c r="F45" s="120"/>
     </row>
-    <row r="46" spans="1:7" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A46" s="109"/>
       <c r="B46" s="5" t="s">
         <v>405</v>
@@ -10642,7 +10651,7 @@
       <c r="E46" s="10"/>
       <c r="F46" s="5"/>
     </row>
-    <row r="47" spans="1:7" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A47" s="109"/>
       <c r="B47" s="5" t="s">
         <v>407</v>
@@ -10652,7 +10661,7 @@
       <c r="E47" s="10"/>
       <c r="F47" s="5"/>
     </row>
-    <row r="48" spans="1:7" s="4" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A48" s="109"/>
       <c r="B48" s="5" t="s">
         <v>408</v>
@@ -10664,11 +10673,18 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="D1:F5"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="A10:F11"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="A15:A20"/>
+    <mergeCell ref="B15:B20"/>
+    <mergeCell ref="C15:C20"/>
+    <mergeCell ref="E15:E20"/>
+    <mergeCell ref="F15:F20"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="E27:E28"/>
@@ -10676,18 +10692,11 @@
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="F30:F31"/>
     <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A15:A20"/>
-    <mergeCell ref="B15:B20"/>
-    <mergeCell ref="C15:C20"/>
-    <mergeCell ref="E15:E20"/>
-    <mergeCell ref="F15:F20"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="D1:F5"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="A10:F11"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B41:F41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
